--- a/media/exports/reports/2026-09/job-margins.xlsx
+++ b/media/exports/reports/2026-09/job-margins.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1230,172 +1230,204 @@
         </is>
       </c>
     </row>
-    <row r="78"/>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Technician time charged, September</t>
+        </is>
+      </c>
+      <c r="B78" s="8">
+        <f>Workings!B354</f>
+        <v/>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>69.2% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Materials charged, September</t>
+        </is>
+      </c>
+      <c r="B79" s="8">
+        <f>Workings!B366</f>
+        <v/>
+      </c>
+      <c r="C79" s="9" t="inlineStr">
+        <is>
+          <t>$7,380 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80"/>
+    <row r="81">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>Job gross margin on call-outs by length, September 2026</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr"/>
-      <c r="B80" s="7" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr"/>
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C80" s="7" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (6)</t>
-        </is>
-      </c>
-      <c r="B81" s="8">
-        <f>Workings!B353</f>
-        <v/>
-      </c>
-      <c r="C81" s="11">
-        <f>Workings!B352</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (13)</t>
-        </is>
-      </c>
-      <c r="B82" s="8">
-        <f>Workings!B364</f>
-        <v/>
-      </c>
-      <c r="C82" s="11">
-        <f>Workings!B363</f>
-        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2-hour call-outs (17)</t>
+          <t>1-hour call-outs (6)</t>
         </is>
       </c>
       <c r="B83" s="8">
-        <f>Workings!B375</f>
+        <f>Workings!B379</f>
         <v/>
       </c>
       <c r="C83" s="11">
-        <f>Workings!B374</f>
+        <f>Workings!B378</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (8)</t>
+          <t>1.5-hour call-outs (13)</t>
         </is>
       </c>
       <c r="B84" s="8">
-        <f>Workings!B386</f>
+        <f>Workings!B392</f>
         <v/>
       </c>
       <c r="C84" s="11">
-        <f>Workings!B385</f>
+        <f>Workings!B391</f>
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3-hour call-outs (11)</t>
+          <t>2-hour call-outs (17)</t>
         </is>
       </c>
       <c r="B85" s="8">
-        <f>Workings!B397</f>
+        <f>Workings!B405</f>
         <v/>
       </c>
       <c r="C85" s="11">
-        <f>Workings!B396</f>
+        <f>Workings!B404</f>
         <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>2.5-hour call-outs (8)</t>
+        </is>
+      </c>
+      <c r="B86" s="8">
+        <f>Workings!B418</f>
+        <v/>
+      </c>
+      <c r="C86" s="11">
+        <f>Workings!B417</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (11)</t>
+        </is>
+      </c>
+      <c r="B87" s="8">
+        <f>Workings!B431</f>
+        <v/>
+      </c>
+      <c r="C87" s="11">
+        <f>Workings!B430</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>4-hour call-outs (9)</t>
         </is>
       </c>
-      <c r="B86" s="8">
-        <f>Workings!B408</f>
-        <v/>
-      </c>
-      <c r="C86" s="11">
-        <f>Workings!B407</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87"/>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="B88" s="8">
+        <f>Workings!B444</f>
+        <v/>
+      </c>
+      <c r="C88" s="11">
+        <f>Workings!B443</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89"/>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="45" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>64 call-outs in September made a 43.9% job gross margin between them. Gross margins run from 37.6% to 47.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90"/>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+    <row r="91" ht="60" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>64 call-outs in September billed $21,543 of technician time and $9,594 of materials ($7,380 at cost plus 30%), and made a 43.9% job gross margin between them. Gross margins run from 37.6% to 47.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Call-outs: 43.9% gross margin, 12.7 points clear of the 31.1% overheads need.</t>
         </is>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="12" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A94:D94"/>
     <mergeCell ref="A70:D70"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A91:D91"/>
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A51:D51"/>
@@ -1427,7 +1459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C411"/>
+  <dimension ref="A1:C447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -4286,14 +4318,14 @@
     <row r="345">
       <c r="A345" s="5" t="inlineStr">
         <is>
-          <t>1-hour call-outs (6)</t>
+          <t>Call-out revenue, September</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="12" t="inlineStr">
         <is>
-          <t>Call-outs of this length in September, added together</t>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -4308,498 +4340,818 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B348" s="13" t="n">
-        <v>6</v>
+        <v>21543</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Materials at cost</t>
         </is>
       </c>
       <c r="B349" s="13" t="n">
-        <v>1793</v>
+        <v>7380</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B350" s="13" t="n">
-        <v>-710</v>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B350" s="14" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B351" s="13" t="n">
-        <v>-408</v>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B351" s="13">
+        <f>B349*(1+B350)</f>
+        <v/>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B352" s="13">
-        <f>B349+B350+B351</f>
-        <v/>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B352" s="13" t="n">
+        <v>9594</v>
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B353" s="16">
-        <f>B352/B349</f>
-        <v/>
-      </c>
-    </row>
-    <row r="354"/>
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B353" s="13">
+        <f>B348+B352</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B354" s="16">
+        <f>B348/B353</f>
+        <v/>
+      </c>
+    </row>
     <row r="355"/>
-    <row r="356">
-      <c r="A356" s="5" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (13)</t>
-        </is>
-      </c>
-    </row>
+    <row r="356"/>
     <row r="357">
-      <c r="A357" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in September, added together</t>
+      <c r="A357" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, September</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="6" t="inlineStr"/>
-      <c r="B358" s="7" t="inlineStr">
+      <c r="A358" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="6" t="inlineStr"/>
+      <c r="B359" s="7" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B359" s="13" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B360" s="13" t="n">
-        <v>4667</v>
+        <v>21543</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Materials at cost</t>
         </is>
       </c>
       <c r="B361" s="13" t="n">
-        <v>-1410</v>
+        <v>7380</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B362" s="13" t="n">
-        <v>-1326</v>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B362" s="14" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
       <c r="B363" s="13">
-        <f>B360+B361+B362</f>
+        <f>B361*(1+B362)</f>
         <v/>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B364" s="16">
-        <f>B363/B360</f>
-        <v/>
-      </c>
-    </row>
-    <row r="365"/>
-    <row r="366"/>
-    <row r="367">
-      <c r="A367" s="5" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (17)</t>
-        </is>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" s="12" t="inlineStr">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B364" s="13" t="n">
+        <v>9594</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B365" s="13">
+        <f>B360+B364</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B366" s="16">
+        <f>B360/B365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in September, added together</t>
         </is>
       </c>
     </row>
-    <row r="369">
-      <c r="A369" s="6" t="inlineStr"/>
-      <c r="B369" s="7" t="inlineStr">
+    <row r="371">
+      <c r="A371" s="6" t="inlineStr"/>
+      <c r="B371" s="7" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B370" s="13" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B371" s="13" t="n">
-        <v>7790</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Call-outs</t>
         </is>
       </c>
       <c r="B372" s="13" t="n">
-        <v>-2200</v>
+        <v>6</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B373" s="13" t="n">
-        <v>-2312</v>
+        <v>870</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B374" s="13" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B375" s="13">
+        <f>B373+B374</f>
+        <v/>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B376" s="13" t="n">
+        <v>-710</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B377" s="13" t="n">
+        <v>-408</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B374" s="13">
-        <f>B371+B372+B373</f>
-        <v/>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" s="15" t="inlineStr">
+      <c r="B378" s="13">
+        <f>B375+B376+B377</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B375" s="16">
-        <f>B374/B371</f>
-        <v/>
-      </c>
-    </row>
-    <row r="376"/>
-    <row r="377"/>
-    <row r="378">
-      <c r="A378" s="5" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="12" t="inlineStr">
+      <c r="B379" s="16">
+        <f>B378/B375</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382">
+      <c r="A382" s="5" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in September, added together</t>
         </is>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" s="6" t="inlineStr"/>
-      <c r="B380" s="7" t="inlineStr">
+    <row r="384">
+      <c r="A384" s="6" t="inlineStr"/>
+      <c r="B384" s="7" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B381" s="13" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B382" s="13" t="n">
-        <v>3996</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B383" s="13" t="n">
-        <v>-840</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B384" s="13" t="n">
-        <v>-1360</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B385" s="13" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B386" s="13" t="n">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B387" s="13" t="n">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B388" s="13">
+        <f>B386+B387</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B389" s="13" t="n">
+        <v>-1410</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B390" s="13" t="n">
+        <v>-1326</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B385" s="13">
-        <f>B382+B383+B384</f>
-        <v/>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" s="15" t="inlineStr">
+      <c r="B391" s="13">
+        <f>B388+B389+B390</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B386" s="16">
-        <f>B385/B382</f>
-        <v/>
-      </c>
-    </row>
-    <row r="387"/>
-    <row r="388"/>
-    <row r="389">
-      <c r="A389" s="5" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" s="12" t="inlineStr">
+      <c r="B392" s="16">
+        <f>B391/B388</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395">
+      <c r="A395" s="5" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in September, added together</t>
         </is>
       </c>
     </row>
-    <row r="391">
-      <c r="A391" s="6" t="inlineStr"/>
-      <c r="B391" s="7" t="inlineStr">
+    <row r="397">
+      <c r="A397" s="6" t="inlineStr"/>
+      <c r="B397" s="7" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
     </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
+    <row r="398">
+      <c r="A398" t="inlineStr">
         <is>
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B392" s="13" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
+      <c r="B398" s="13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B399" s="13" t="n">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B400" s="13" t="n">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B393" s="13" t="n">
-        <v>6358</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B394" s="13" t="n">
-        <v>-1210</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B395" s="13" t="n">
-        <v>-2244</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B396" s="13">
-        <f>B393+B394+B395</f>
-        <v/>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B397" s="16">
-        <f>B396/B393</f>
-        <v/>
-      </c>
-    </row>
-    <row r="398"/>
-    <row r="399"/>
-    <row r="400">
-      <c r="A400" s="5" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in September, added together</t>
-        </is>
+      <c r="B401" s="13">
+        <f>B399+B400</f>
+        <v/>
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="6" t="inlineStr"/>
-      <c r="B402" s="7" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B402" s="13" t="n">
+        <v>-2200</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time at cost</t>
         </is>
       </c>
       <c r="B403" s="13" t="n">
-        <v>9</v>
+        <v>-2312</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B404" s="13">
+        <f>B401+B402+B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B405" s="16">
+        <f>B404/B401</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408">
+      <c r="A408" s="5" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in September, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="6" t="inlineStr"/>
+      <c r="B410" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B411" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B412" s="13" t="n">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B413" s="13" t="n">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B404" s="13" t="n">
-        <v>6533</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B405" s="13" t="n">
+      <c r="B414" s="13">
+        <f>B412+B413</f>
+        <v/>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B415" s="13" t="n">
+        <v>-840</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B416" s="13" t="n">
+        <v>-1360</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B417" s="13">
+        <f>B414+B415+B416</f>
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B418" s="16">
+        <f>B417/B414</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421">
+      <c r="A421" s="5" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in September, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="6" t="inlineStr"/>
+      <c r="B423" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B424" s="13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B425" s="13" t="n">
+        <v>4785</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B426" s="13" t="n">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B427" s="13">
+        <f>B425+B426</f>
+        <v/>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B428" s="13" t="n">
+        <v>-1210</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B429" s="13" t="n">
+        <v>-2244</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B430" s="13">
+        <f>B427+B428+B429</f>
+        <v/>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B431" s="16">
+        <f>B430/B427</f>
+        <v/>
+      </c>
+    </row>
+    <row r="432"/>
+    <row r="433"/>
+    <row r="434">
+      <c r="A434" s="5" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in September, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="6" t="inlineStr"/>
+      <c r="B436" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B437" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B438" s="13" t="n">
+        <v>5220</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B439" s="13" t="n">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B440" s="13">
+        <f>B438+B439</f>
+        <v/>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B441" s="13" t="n">
         <v>-1010</v>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
+    <row r="442">
+      <c r="A442" t="inlineStr">
         <is>
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B406" s="13" t="n">
+      <c r="B442" s="13" t="n">
         <v>-2448</v>
       </c>
     </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
+    <row r="443">
+      <c r="A443" t="inlineStr">
         <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B407" s="13">
-        <f>B404+B405+B406</f>
-        <v/>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" s="15" t="inlineStr">
+      <c r="B443" s="13">
+        <f>B440+B441+B442</f>
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B408" s="16">
-        <f>B407/B404</f>
-        <v/>
-      </c>
-    </row>
-    <row r="409"/>
-    <row r="410"/>
-    <row r="411"/>
+      <c r="B444" s="16">
+        <f>B443/B440</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -4812,7 +5164,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="15" manualBreakCount="15">
+  <rowBreaks count="17" manualBreakCount="17">
     <brk id="30" min="0" max="16383" man="1"/>
     <brk id="57" min="0" max="16383" man="1"/>
     <brk id="79" min="0" max="16383" man="1"/>
@@ -4826,8 +5178,10 @@
     <brk id="283" min="0" max="16383" man="1"/>
     <brk id="309" min="0" max="16383" man="1"/>
     <brk id="335" min="0" max="16383" man="1"/>
-    <brk id="366" min="0" max="16383" man="1"/>
-    <brk id="388" min="0" max="16383" man="1"/>
+    <brk id="356" min="0" max="16383" man="1"/>
+    <brk id="381" min="0" max="16383" man="1"/>
+    <brk id="407" min="0" max="16383" man="1"/>
+    <brk id="433" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/media/exports/reports/2026-09/job-margins.xlsx
+++ b/media/exports/reports/2026-09/job-margins.xlsx
@@ -25,48 +25,58 @@
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0;[Red](#,##0.0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
@@ -99,36 +109,36 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1438,8 +1448,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5157,8 +5167,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8244,8 +8254,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-09/job-margins.xlsx
+++ b/media/exports/reports/2026-09/job-margins.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D99"/>
+  <dimension ref="A1:D107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Before overheads, so this is not profit. Pick a type of job and every number, chart and note on the page follows it.</t>
+          <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Pick a type of job and every number, chart and note on the page follows it.</t>
         </is>
       </c>
     </row>
@@ -615,232 +615,236 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>August 41.1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Job gross margin, August · All jobs</t>
+        </is>
+      </c>
+      <c r="B16" s="8">
+        <f>Workings!B37</f>
+        <v/>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>Workings!B53</f>
+        <v/>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (September)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Job gross margin by type of job, September 2026</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B19" s="8">
-        <f>Workings!B37</f>
-        <v/>
-      </c>
-      <c r="C19" s="11">
-        <f>Workings!B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Installations</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>Workings!B46</f>
-        <v/>
-      </c>
-      <c r="C20" s="11">
-        <f>Workings!B45</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>Workings!B63</f>
+        <v/>
+      </c>
+      <c r="C21" s="11">
+        <f>Workings!B62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Installations</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>Workings!B72</f>
+        <v/>
+      </c>
+      <c r="C22" s="11">
+        <f>Workings!B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B21" s="8">
-        <f>Workings!B55</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>Workings!B54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B23" s="8">
+        <f>Workings!B81</f>
+        <v/>
+      </c>
+      <c r="C23" s="11">
+        <f>Workings!B80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>In September maintenance contracts made a 59.5% job gross margin, installations made a 27.0% job gross margin, call-outs and repairs made a 43.9% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 31.1% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance contracts: 59.5% gross margin, the most profitable work you do. Installations: 27.0% gross margin, below the 31.1% needed to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Installations: 27.0% gross margin, 8.0 points under the 35.0% target: about $10,413 on $130,700 of revenue in September. It's below the 31.1% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in September).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Type of job: Maintenance contracts</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Job gross margin, September · Maintenance contracts</t>
         </is>
       </c>
-      <c r="B31" s="8">
-        <f>Workings!B64</f>
-        <v/>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>August 59.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each maintenance contract, September 2026</t>
+      <c r="B33" s="8">
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Job gross margin, August · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B34" s="8">
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Carindale vet clinic</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B35" s="8">
-        <f>Workings!B77</f>
-        <v/>
-      </c>
-      <c r="C35" s="11">
-        <f>Workings!B76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B36" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C36" s="11">
-        <f>Workings!B89</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B115</f>
+        <v/>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (September)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B37" s="8">
-        <f>Workings!B103</f>
-        <v/>
-      </c>
-      <c r="C37" s="11">
-        <f>Workings!B102</f>
-        <v/>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each maintenance contract, September 2026</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Ashgrove aged care</t>
-        </is>
-      </c>
-      <c r="B38" s="8">
-        <f>Workings!B116</f>
-        <v/>
-      </c>
-      <c r="C38" s="11">
-        <f>Workings!B115</f>
-        <v/>
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Carindale vet clinic</t>
         </is>
       </c>
       <c r="B39" s="8">
@@ -855,7 +859,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
       <c r="B40" s="8">
@@ -870,7 +874,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B41" s="8">
@@ -885,7 +889,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B42" s="8">
@@ -900,7 +904,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B43" s="8">
@@ -915,7 +919,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
       <c r="B44" s="8">
@@ -930,7 +934,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B45" s="8">
@@ -945,7 +949,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Chermside retail centre</t>
         </is>
       </c>
       <c r="B46" s="8">
@@ -960,7 +964,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Wacol logistics depot</t>
         </is>
       </c>
       <c r="B47" s="8">
@@ -975,7 +979,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B48" s="8">
@@ -987,462 +991,586 @@
         <v/>
       </c>
     </row>
-    <row r="49"/>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B49" s="8">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C49" s="11">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B50" s="8">
+        <f>Workings!B272</f>
+        <v/>
+      </c>
+      <c r="C50" s="11">
+        <f>Workings!B271</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B51" s="8">
+        <f>Workings!B285</f>
+        <v/>
+      </c>
+      <c r="C51" s="11">
+        <f>Workings!B284</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Kangaroo Point townhouses</t>
+        </is>
+      </c>
+      <c r="B52" s="8">
+        <f>Workings!B298</f>
+        <v/>
+      </c>
+      <c r="C52" s="11">
+        <f>Workings!B297</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>All 14 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>The Kangaroo Point townhouses contract: 58.2% gross margin, 27.1 points clear of the 31.1% overheads need. Maintenance contracts overall: 59.5% gross margin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Job gross margin, September · Installations</t>
-        </is>
-      </c>
-      <c r="B58" s="8">
-        <f>Workings!B255</f>
-        <v/>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>August 33.6%</t>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in September). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in September).</t>
         </is>
       </c>
     </row>
     <row r="59"/>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each installation invoiced in September 2026</t>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Installations</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr"/>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Gross margin $</t>
+          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bulimba EV chargers</t>
+          <t>Job gross margin, September · Installations</t>
         </is>
       </c>
       <c r="B62" s="8">
-        <f>Workings!B268</f>
-        <v/>
-      </c>
-      <c r="C62" s="11">
-        <f>Workings!B267</f>
-        <v/>
+        <f>Workings!B307</f>
+        <v/>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Milton office LED lighting</t>
+          <t>Job gross margin, August · Installations</t>
         </is>
       </c>
       <c r="B63" s="8">
-        <f>Workings!B281</f>
-        <v/>
-      </c>
-      <c r="C63" s="11">
-        <f>Workings!B280</f>
-        <v/>
+        <f>Workings!B316</f>
+        <v/>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B64" s="8">
+        <f>Workings!B332</f>
+        <v/>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (September)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each installation invoiced in September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr"/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Bulimba EV chargers</t>
+        </is>
+      </c>
+      <c r="B68" s="8">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C68" s="11">
+        <f>Workings!B345</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Milton office LED lighting</t>
+        </is>
+      </c>
+      <c r="B69" s="8">
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C69" s="11">
+        <f>Workings!B358</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>Chermside clinic cabling</t>
         </is>
       </c>
-      <c r="B64" s="8">
-        <f>Workings!B294</f>
-        <v/>
-      </c>
-      <c r="C64" s="11">
-        <f>Workings!B293</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="B70" s="8">
+        <f>Workings!B372</f>
+        <v/>
+      </c>
+      <c r="C70" s="11">
+        <f>Workings!B371</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>West End cafe air-con</t>
         </is>
       </c>
-      <c r="B65" s="8">
-        <f>Workings!B307</f>
-        <v/>
-      </c>
-      <c r="C65" s="11">
-        <f>Workings!B306</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="B71" s="8">
+        <f>Workings!B385</f>
+        <v/>
+      </c>
+      <c r="C71" s="11">
+        <f>Workings!B384</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>Carindale solar and battery</t>
         </is>
       </c>
-      <c r="B66" s="8">
-        <f>Workings!B320</f>
-        <v/>
-      </c>
-      <c r="C66" s="11">
-        <f>Workings!B319</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="B72" s="8">
+        <f>Workings!B398</f>
+        <v/>
+      </c>
+      <c r="C72" s="11">
+        <f>Workings!B397</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>Wacol warehouse switchboard</t>
         </is>
       </c>
-      <c r="B67" s="8">
-        <f>Workings!B333</f>
-        <v/>
-      </c>
-      <c r="C67" s="11">
-        <f>Workings!B332</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68"/>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="60" customHeight="1">
-      <c r="A70" s="3" t="inlineStr">
-        <is>
-          <t>3 of the 6 installation jobs invoiced in September made less than the 35.0% job gross margin target. The Wacol warehouse switchboard made a 13.5% job gross margin: 150.0 h of technician time ($10,200) and $7,400 of subcontractors on a $46,800 job. Jobs need 31.1% gross margin just to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71"/>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Below the 31.1% overheads need: Carindale solar and battery (26.9%), Wacol warehouse switchboard (13.5%). Most profitable: Bulimba EV chargers (45.2%).</t>
-        </is>
+      <c r="B73" s="8">
+        <f>Workings!B411</f>
+        <v/>
+      </c>
+      <c r="C73" s="11">
+        <f>Workings!B410</f>
+        <v/>
       </c>
     </row>
     <row r="74"/>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Job gross margin, September · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B77" s="8">
-        <f>Workings!B342</f>
-        <v/>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>August 43.7%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="60" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>3 of the 6 installation jobs invoiced in September made less than the 35.0% job gross margin target. The Wacol warehouse switchboard made a 13.5% job gross margin: 150.0 h of technician time ($10,200) and $7,400 of subcontractors on a $46,800 job. Jobs need 31.1% gross margin just to cover overheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Technician time charged, September</t>
-        </is>
-      </c>
-      <c r="B78" s="8">
-        <f>Workings!B354</f>
-        <v/>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>69.2% of call-out revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Materials charged, September</t>
-        </is>
-      </c>
-      <c r="B79" s="8">
-        <f>Workings!B366</f>
-        <v/>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>$7,380 at cost, plus 30%</t>
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="60" customHeight="1">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>3 installations under the 35.0% target, worth about $12,497 between them on $87,100 of revenue. The biggest gap, Wacol warehouse switchboard: 13.5% gross margin, 21.5 points under the 35.0% target: about $10,080 on $46,800 of revenue in September. It's below the 31.1% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
     <row r="80"/>
     <row r="81">
-      <c r="A81" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on call-outs by length, September 2026</t>
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Call-outs and repairs</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr"/>
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>Gross margin $</t>
+          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1-hour call-outs (6)</t>
+          <t>Job gross margin, September · Call-outs and repairs</t>
         </is>
       </c>
       <c r="B83" s="8">
-        <f>Workings!B379</f>
-        <v/>
-      </c>
-      <c r="C83" s="11">
-        <f>Workings!B378</f>
-        <v/>
+        <f>Workings!B420</f>
+        <v/>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1.5-hour call-outs (13)</t>
+          <t>Job gross margin, August · Call-outs and repairs</t>
         </is>
       </c>
       <c r="B84" s="8">
-        <f>Workings!B392</f>
-        <v/>
-      </c>
-      <c r="C84" s="11">
-        <f>Workings!B391</f>
-        <v/>
+        <f>Workings!B429</f>
+        <v/>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2-hour call-outs (17)</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B85" s="8">
-        <f>Workings!B405</f>
-        <v/>
-      </c>
-      <c r="C85" s="11">
-        <f>Workings!B404</f>
-        <v/>
+        <f>Workings!B445</f>
+        <v/>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (September)</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (8)</t>
+          <t>Technician time charged, September</t>
         </is>
       </c>
       <c r="B86" s="8">
-        <f>Workings!B418</f>
-        <v/>
-      </c>
-      <c r="C86" s="11">
-        <f>Workings!B417</f>
-        <v/>
+        <f>Workings!B458</f>
+        <v/>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>69.2% of call-out revenue</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>Materials charged, September</t>
+        </is>
+      </c>
+      <c r="B87" s="8">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C87" s="9" t="inlineStr">
+        <is>
+          <t>$7,380 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88"/>
+    <row r="89">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on call-outs by length, September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="inlineStr"/>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (6)</t>
+        </is>
+      </c>
+      <c r="B91" s="8">
+        <f>Workings!B483</f>
+        <v/>
+      </c>
+      <c r="C91" s="11">
+        <f>Workings!B482</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (13)</t>
+        </is>
+      </c>
+      <c r="B92" s="8">
+        <f>Workings!B496</f>
+        <v/>
+      </c>
+      <c r="C92" s="11">
+        <f>Workings!B495</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (17)</t>
+        </is>
+      </c>
+      <c r="B93" s="8">
+        <f>Workings!B509</f>
+        <v/>
+      </c>
+      <c r="C93" s="11">
+        <f>Workings!B508</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (8)</t>
+        </is>
+      </c>
+      <c r="B94" s="8">
+        <f>Workings!B522</f>
+        <v/>
+      </c>
+      <c r="C94" s="11">
+        <f>Workings!B521</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>3-hour call-outs (11)</t>
         </is>
       </c>
-      <c r="B87" s="8">
-        <f>Workings!B431</f>
-        <v/>
-      </c>
-      <c r="C87" s="11">
-        <f>Workings!B430</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
+      <c r="B95" s="8">
+        <f>Workings!B535</f>
+        <v/>
+      </c>
+      <c r="C95" s="11">
+        <f>Workings!B534</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>4-hour call-outs (9)</t>
         </is>
       </c>
-      <c r="B88" s="8">
-        <f>Workings!B444</f>
-        <v/>
-      </c>
-      <c r="C88" s="11">
-        <f>Workings!B443</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89"/>
-    <row r="90">
-      <c r="A90" s="4" t="inlineStr">
+      <c r="B96" s="8">
+        <f>Workings!B548</f>
+        <v/>
+      </c>
+      <c r="C96" s="11">
+        <f>Workings!B547</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="60" customHeight="1">
-      <c r="A91" s="3" t="inlineStr">
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>64 call-outs in September billed $21,543 of technician time and $9,594 of materials ($7,380 at cost plus 30%), and made a 43.9% job gross margin between them. Gross margins run from 37.6% to 47.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="92"/>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>Call-outs: 43.9% gross margin, 12.7 points clear of the 31.1% overheads need.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" s="5" t="inlineStr">
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>All call-outs: 43.9% gross margin, 8.9 points over the 35.0% target ($2,761 ahead on $31,137 in September).</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="12" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="98"/>
-    <row r="99"/>
+    <row r="106"/>
+    <row r="107"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A102:D102"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A94:D94"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A79:D79"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A91:D91"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -1455,10 +1583,11 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="22" min="0" max="16383" man="1"/>
-    <brk id="49" min="0" max="16383" man="1"/>
-    <brk id="75" min="0" max="16383" man="1"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="18" min="0" max="16383" man="1"/>
+    <brk id="36" min="0" max="16383" man="1"/>
+    <brk id="65" min="0" max="16383" man="1"/>
+    <brk id="88" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1469,7 +1598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C447"/>
+  <dimension ref="A1:C551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1735,14 +1864,14 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts, September</t>
+          <t>All lines: gross margin, September and August</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1879,12 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1895,10 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>40500</v>
+        <v>202337</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>179007</v>
       </c>
     </row>
     <row r="35">
@@ -1771,7 +1908,10 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>16384</v>
+        <v>129230</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>105370</v>
       </c>
     </row>
     <row r="36">
@@ -1784,6 +1924,10 @@
         <f>B34-B35</f>
         <v/>
       </c>
+      <c r="C36" s="13">
+        <f>C34-C35</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
@@ -1793,6 +1937,10 @@
       </c>
       <c r="B37" s="16">
         <f>B36/B34</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f>C36/C34</f>
         <v/>
       </c>
     </row>
@@ -1801,14 +1949,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Installations, September</t>
+          <t>From gross margin to profit, September 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
@@ -1823,407 +1971,406 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Gross margin on jobs</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>130700</v>
+        <v>73107</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Technician wages and on-costs</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>95368</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B45" s="13">
-        <f>B43-B44</f>
-        <v/>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>51170</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B46" s="16">
-        <f>B45/B43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B46" s="13">
+        <f>B44-B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B47" s="13">
+        <f>B43-B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>59580</v>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Call-outs and repairs, September</t>
-        </is>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B49" s="13">
+        <f>B47-B48</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
-        </is>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n">
+        <v>202337</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr"/>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B51" s="14">
+        <f>B43/B50</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B52" s="14">
+        <f>B49/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B53" s="16">
+        <f>(B46+B48)/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance contracts, September</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B52" s="13" t="n">
-        <v>31137</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Direct cost</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="n">
-        <v>17478</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B54" s="13">
-        <f>B52-B53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B55" s="16">
-        <f>B54/B52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance contracts: gross margin, September and August</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr"/>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Sep 26</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Aug 26</t>
-        </is>
+      <c r="B60" s="13" t="n">
+        <v>40500</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>40500</v>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>40500</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Direct cost</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="n">
-        <v>16384</v>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>16384</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B62" s="13">
+        <f>B60-B61</f>
+        <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B63" s="13">
-        <f>B61-B62</f>
-        <v/>
-      </c>
-      <c r="C63" s="13">
-        <f>C61-C62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="inlineStr">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B64" s="16">
-        <f>B63/B61</f>
-        <v/>
-      </c>
-      <c r="C64" s="16">
-        <f>C63/C61</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B63" s="16">
+        <f>B62/B60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65"/>
-    <row r="66"/>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Installations, September</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Carindale vet clinic</t>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+      <c r="A68" s="6" t="inlineStr"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr"/>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="n">
+        <v>130700</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B70" s="13" t="n">
-        <v>1700</v>
+        <v>95368</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="n">
-        <v>-30</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B71" s="13">
+        <f>B69-B70</f>
+        <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B72" s="16">
+        <f>B71/B69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74"/>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B75" s="13">
-        <f>-B73*B74</f>
-        <v/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs, September</t>
+        </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B76" s="13">
-        <f>B70+B71+B72+B75</f>
-        <v/>
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+        </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B77" s="16">
-        <f>B76/B70</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79"/>
+      <c r="A77" s="6" t="inlineStr"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="n">
+        <v>31137</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="n">
+        <v>17478</v>
+      </c>
+    </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B80" s="13">
+        <f>B78-B79</f>
+        <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr"/>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="n">
-        <v>2200</v>
-      </c>
-    </row>
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B81" s="16">
+        <f>B80/B78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83"/>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>-40</v>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance contracts: gross margin, September and August</t>
+        </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="n">
-        <v>0</v>
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="n">
-        <v>12</v>
+      <c r="A86" s="6" t="inlineStr"/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B87" s="13" t="n">
-        <v>68</v>
+        <v>40500</v>
+      </c>
+      <c r="C87" s="13" t="n">
+        <v>40500</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B88" s="13">
-        <f>-B86*B87</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C88" s="13" t="n">
+        <v>16384</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B89" s="13">
-        <f>B83+B84+B85+B88</f>
+        <f>B87-B88</f>
+        <v/>
+      </c>
+      <c r="C89" s="13">
+        <f>C87-C88</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t>Job gross margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B90" s="16">
-        <f>B89/B83</f>
+        <f>B89/B87</f>
+        <v/>
+      </c>
+      <c r="C90" s="16">
+        <f>C89/C87</f>
         <v/>
       </c>
     </row>
@@ -2232,14 +2379,14 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Maintenance contracts: gross margin, September and August</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -2247,7 +2394,12 @@
       <c r="A95" s="6" t="inlineStr"/>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>This job</t>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
         </is>
       </c>
     </row>
@@ -2258,187 +2410,200 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>1800</v>
+        <v>40500</v>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>40500</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>-40</v>
+        <v>16384</v>
+      </c>
+      <c r="C97" s="13" t="n">
+        <v>16384</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="n">
-        <v>0</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B98" s="13">
+        <f>B96-B97</f>
+        <v/>
+      </c>
+      <c r="C98" s="13">
+        <f>C96-C97</f>
+        <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B100" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B101" s="13">
-        <f>-B99*B100</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B99" s="16">
+        <f>B98/B96</f>
+        <v/>
+      </c>
+      <c r="C99" s="16">
+        <f>C98/C96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101"/>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B102" s="13">
-        <f>B96+B97+B98+B101</f>
-        <v/>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, September 2026</t>
+        </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B103" s="16">
-        <f>B102/B96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105"/>
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr"/>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="n">
+        <v>73107</v>
+      </c>
+    </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Ashgrove aged care</t>
-        </is>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="n">
+        <v>54600</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="n">
+        <v>51170</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr"/>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B108" s="13">
+        <f>B106-B107</f>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B109" s="13" t="n">
-        <v>3600</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B109" s="13">
+        <f>B105-B108</f>
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
       <c r="B110" s="13" t="n">
-        <v>-80</v>
+        <v>59580</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B111" s="13" t="n">
-        <v>0</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B111" s="13">
+        <f>B109-B110</f>
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B112" s="17" t="n">
-        <v>20</v>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="n">
+        <v>202337</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B113" s="13" t="n">
-        <v>68</v>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B113" s="14">
+        <f>B105/B112</f>
+        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B114" s="13">
-        <f>-B112*B113</f>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B114" s="14">
+        <f>B111/B112</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B115" s="13">
-        <f>B109+B110+B111+B114</f>
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B115" s="16">
+        <f>(B108+B110)/B112</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B116" s="16">
-        <f>B115/B109</f>
-        <v/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
       </c>
     </row>
     <row r="117"/>
@@ -2446,7 +2611,7 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Carindale vet clinic</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2637,7 @@
         </is>
       </c>
       <c r="B122" s="13" t="n">
-        <v>3400</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="123">
@@ -2482,7 +2647,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>-70</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="124">
@@ -2502,7 +2667,7 @@
         </is>
       </c>
       <c r="B125" s="17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126">
@@ -2553,7 +2718,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2744,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>3200</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="136">
@@ -2589,7 +2754,7 @@
         </is>
       </c>
       <c r="B136" s="13" t="n">
-        <v>-60</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="137">
@@ -2609,7 +2774,7 @@
         </is>
       </c>
       <c r="B138" s="17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139">
@@ -2660,7 +2825,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2851,7 @@
         </is>
       </c>
       <c r="B148" s="13" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="149">
@@ -2696,7 +2861,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="150">
@@ -2716,7 +2881,7 @@
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152">
@@ -2767,7 +2932,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2958,7 @@
         </is>
       </c>
       <c r="B161" s="13" t="n">
-        <v>4100</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="162">
@@ -2803,7 +2968,7 @@
         </is>
       </c>
       <c r="B162" s="13" t="n">
-        <v>-100</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="163">
@@ -2823,7 +2988,7 @@
         </is>
       </c>
       <c r="B164" s="17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165">
@@ -2874,7 +3039,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
@@ -2900,7 +3065,7 @@
         </is>
       </c>
       <c r="B174" s="13" t="n">
-        <v>3000</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="175">
@@ -2930,7 +3095,7 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178">
@@ -2981,7 +3146,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3172,7 @@
         </is>
       </c>
       <c r="B187" s="13" t="n">
-        <v>4200</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="188">
@@ -3017,7 +3182,7 @@
         </is>
       </c>
       <c r="B188" s="13" t="n">
-        <v>-90</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="189">
@@ -3037,7 +3202,7 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="191">
@@ -3088,7 +3253,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Newstead gym</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3279,7 @@
         </is>
       </c>
       <c r="B200" s="13" t="n">
-        <v>2800</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="201">
@@ -3124,7 +3289,7 @@
         </is>
       </c>
       <c r="B201" s="13" t="n">
-        <v>-60</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="202">
@@ -3144,7 +3309,7 @@
         </is>
       </c>
       <c r="B203" s="17" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204">
@@ -3195,7 +3360,7 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Chermside retail centre</t>
         </is>
       </c>
     </row>
@@ -3221,7 +3386,7 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>2600</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="214">
@@ -3231,7 +3396,7 @@
         </is>
       </c>
       <c r="B214" s="13" t="n">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="215">
@@ -3251,7 +3416,7 @@
         </is>
       </c>
       <c r="B216" s="17" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217">
@@ -3302,7 +3467,7 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Wacol logistics depot</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3493,7 @@
         </is>
       </c>
       <c r="B226" s="13" t="n">
-        <v>3900</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="227">
@@ -3338,7 +3503,7 @@
         </is>
       </c>
       <c r="B227" s="13" t="n">
-        <v>-110</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="228">
@@ -3358,7 +3523,7 @@
         </is>
       </c>
       <c r="B229" s="17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="230">
@@ -3409,7 +3574,7 @@
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Milton office tower</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3600,7 @@
         </is>
       </c>
       <c r="B239" s="13" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="240">
@@ -3445,7 +3610,7 @@
         </is>
       </c>
       <c r="B240" s="13" t="n">
-        <v>-50</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="241">
@@ -3465,7 +3630,7 @@
         </is>
       </c>
       <c r="B242" s="17" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="243">
@@ -3516,14 +3681,14 @@
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, September and August</t>
+          <t>Bulimba school</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3531,12 +3696,7 @@
       <c r="A251" s="6" t="inlineStr"/>
       <c r="B251" s="7" t="inlineStr">
         <is>
-          <t>Sep 26</t>
-        </is>
-      </c>
-      <c r="C251" s="7" t="inlineStr">
-        <is>
-          <t>Aug 26</t>
+          <t>This job</t>
         </is>
       </c>
     </row>
@@ -3547,480 +3707,485 @@
         </is>
       </c>
       <c r="B252" s="13" t="n">
-        <v>130700</v>
-      </c>
-      <c r="C252" s="13" t="n">
-        <v>109600</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B253" s="13" t="n">
-        <v>95368</v>
-      </c>
-      <c r="C253" s="13" t="n">
-        <v>72720</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B254" s="13">
-        <f>B252-B253</f>
-        <v/>
-      </c>
-      <c r="C254" s="13">
-        <f>C252-C253</f>
-        <v/>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B254" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B255" s="16">
-        <f>B254/B252</f>
-        <v/>
-      </c>
-      <c r="C255" s="16">
-        <f>C254/C252</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256"/>
-    <row r="257"/>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B255" s="17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B256" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B257" s="13">
+        <f>-B255*B256</f>
+        <v/>
+      </c>
+    </row>
     <row r="258">
-      <c r="A258" s="5" t="inlineStr">
-        <is>
-          <t>Bulimba EV chargers</t>
-        </is>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B258" s="13">
+        <f>B252+B253+B254+B257</f>
+        <v/>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="12" t="inlineStr">
+      <c r="A259" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B259" s="16">
+        <f>B258/B252</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="6" t="inlineStr"/>
-      <c r="B260" s="7" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr"/>
+      <c r="B264" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B261" s="13" t="n">
-        <v>9800</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B262" s="13" t="n">
-        <v>-3600</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B263" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B264" s="17" t="n">
-        <v>26</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B265" s="13" t="n">
-        <v>68</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B266" s="13">
-        <f>-B264*B265</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B266" s="13" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B267" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B268" s="17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B269" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B270" s="13">
+        <f>-B268*B269</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B267" s="13">
-        <f>B261+B262+B263+B266</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="15" t="inlineStr">
+      <c r="B271" s="13">
+        <f>B265+B266+B267+B270</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B268" s="16">
-        <f>B267/B261</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Milton office LED lighting</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="12" t="inlineStr">
+      <c r="B272" s="16">
+        <f>B271/B265</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="6" t="inlineStr"/>
-      <c r="B273" s="7" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="6" t="inlineStr"/>
+      <c r="B277" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B274" s="13" t="n">
-        <v>18600</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B275" s="13" t="n">
-        <v>-6900</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B276" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B277" s="17" t="n">
-        <v>64</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B278" s="13" t="n">
-        <v>68</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B279" s="13">
-        <f>-B277*B278</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B279" s="13" t="n">
+        <v>-110</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B280" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B281" s="17" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B282" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B283" s="13">
+        <f>-B281*B282</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B280" s="13">
-        <f>B274+B275+B276+B279</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="15" t="inlineStr">
+      <c r="B284" s="13">
+        <f>B278+B279+B280+B283</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B281" s="16">
-        <f>B280/B274</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284">
-      <c r="A284" s="5" t="inlineStr">
-        <is>
-          <t>Chermside clinic cabling</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="12" t="inlineStr">
+      <c r="B285" s="16">
+        <f>B284/B278</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288">
+      <c r="A288" s="5" t="inlineStr">
+        <is>
+          <t>Kangaroo Point townhouses</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="6" t="inlineStr"/>
-      <c r="B286" s="7" t="inlineStr">
+    <row r="290">
+      <c r="A290" s="6" t="inlineStr"/>
+      <c r="B290" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B287" s="13" t="n">
-        <v>15200</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B288" s="13" t="n">
-        <v>-4300</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B289" s="13" t="n">
-        <v>-1800</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B290" s="17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B291" s="13" t="n">
-        <v>68</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B292" s="13">
-        <f>-B290*B291</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B292" s="13" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B293" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B294" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B295" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B296" s="13">
+        <f>-B294*B295</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B293" s="13">
-        <f>B287+B288+B289+B292</f>
-        <v/>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="15" t="inlineStr">
+      <c r="B297" s="13">
+        <f>B291+B292+B293+B296</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B294" s="16">
-        <f>B293/B287</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>West End cafe air-con</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="6" t="inlineStr"/>
-      <c r="B299" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B300" s="13" t="n">
-        <v>12900</v>
-      </c>
-    </row>
+      <c r="B298" s="16">
+        <f>B297/B291</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299"/>
+    <row r="300"/>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B301" s="13" t="n">
-        <v>-5100</v>
+      <c r="A301" s="5" t="inlineStr">
+        <is>
+          <t>Installations: gross margin, September and August</t>
+        </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B302" s="13" t="n">
-        <v>-900</v>
+      <c r="A302" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B303" s="17" t="n">
-        <v>38</v>
+      <c r="A303" s="6" t="inlineStr"/>
+      <c r="B303" s="7" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="C303" s="7" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B304" s="13" t="n">
-        <v>68</v>
+        <v>130700</v>
+      </c>
+      <c r="C304" s="13" t="n">
+        <v>109600</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B305" s="13">
-        <f>-B303*B304</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B305" s="13" t="n">
+        <v>95368</v>
+      </c>
+      <c r="C305" s="13" t="n">
+        <v>72720</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B306" s="13">
-        <f>B300+B301+B302+B305</f>
+        <f>B304-B305</f>
+        <v/>
+      </c>
+      <c r="C306" s="13">
+        <f>C304-C305</f>
         <v/>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="15" t="inlineStr">
         <is>
-          <t>Job gross margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B307" s="16">
-        <f>B306/B300</f>
+        <f>B306/B304</f>
+        <v/>
+      </c>
+      <c r="C307" s="16">
+        <f>C306/C304</f>
         <v/>
       </c>
     </row>
@@ -4029,14 +4194,14 @@
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>Carindale solar and battery</t>
+          <t>Installations: gross margin, September and August</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="12" t="inlineStr">
         <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4209,12 @@
       <c r="A312" s="6" t="inlineStr"/>
       <c r="B312" s="7" t="inlineStr">
         <is>
-          <t>This job</t>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="C312" s="7" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
         </is>
       </c>
     </row>
@@ -4055,187 +4225,200 @@
         </is>
       </c>
       <c r="B313" s="13" t="n">
-        <v>27400</v>
+        <v>130700</v>
+      </c>
+      <c r="C313" s="13" t="n">
+        <v>109600</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B314" s="13" t="n">
-        <v>-13800</v>
+        <v>95368</v>
+      </c>
+      <c r="C314" s="13" t="n">
+        <v>72720</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B315" s="13" t="n">
-        <v>-3100</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B315" s="13">
+        <f>B313-B314</f>
+        <v/>
+      </c>
+      <c r="C315" s="13">
+        <f>C313-C314</f>
+        <v/>
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B316" s="17" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B317" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="318">
-      <c r="A318" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B318" s="13">
-        <f>-B316*B317</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A316" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B316" s="16">
+        <f>B315/B313</f>
+        <v/>
+      </c>
+      <c r="C316" s="16">
+        <f>C315/C313</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317"/>
+    <row r="318"/>
     <row r="319">
-      <c r="A319" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B319" s="13">
-        <f>B313+B314+B315+B318</f>
-        <v/>
+      <c r="A319" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, September 2026</t>
+        </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B320" s="16">
-        <f>B319/B313</f>
-        <v/>
-      </c>
-    </row>
-    <row r="321"/>
-    <row r="322"/>
+      <c r="A320" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="6" t="inlineStr"/>
+      <c r="B321" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B322" s="13" t="n">
+        <v>73107</v>
+      </c>
+    </row>
     <row r="323">
-      <c r="A323" s="5" t="inlineStr">
-        <is>
-          <t>Wacol warehouse switchboard</t>
-        </is>
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B323" s="13" t="n">
+        <v>54600</v>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B324" s="13" t="n">
+        <v>51170</v>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="6" t="inlineStr"/>
-      <c r="B325" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B325" s="13">
+        <f>B323-B324</f>
+        <v/>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B326" s="13" t="n">
-        <v>46800</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B326" s="13">
+        <f>B322-B325</f>
+        <v/>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
       <c r="B327" s="13" t="n">
-        <v>-22900</v>
+        <v>59580</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B328" s="13" t="n">
-        <v>-7400</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B328" s="13">
+        <f>B326-B327</f>
+        <v/>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B329" s="17" t="n">
-        <v>150</v>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B329" s="13" t="n">
+        <v>202337</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B330" s="13" t="n">
-        <v>68</v>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B330" s="14">
+        <f>B322/B329</f>
+        <v/>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B331" s="13">
-        <f>-B329*B330</f>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B331" s="14">
+        <f>B328/B329</f>
         <v/>
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B332" s="13">
-        <f>B326+B327+B328+B331</f>
+      <c r="A332" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B332" s="16">
+        <f>(B325+B327)/B329</f>
         <v/>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B333" s="16">
-        <f>B332/B326</f>
-        <v/>
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
       </c>
     </row>
     <row r="334"/>
@@ -4243,14 +4426,14 @@
     <row r="336">
       <c r="A336" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, September and August</t>
+          <t>Bulimba EV chargers</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4441,7 @@
       <c r="A338" s="6" t="inlineStr"/>
       <c r="B338" s="7" t="inlineStr">
         <is>
-          <t>Sep 26</t>
-        </is>
-      </c>
-      <c r="C338" s="7" t="inlineStr">
-        <is>
-          <t>Aug 26</t>
+          <t>This job</t>
         </is>
       </c>
     </row>
@@ -4274,894 +4452,1773 @@
         </is>
       </c>
       <c r="B339" s="13" t="n">
-        <v>31137</v>
-      </c>
-      <c r="C339" s="13" t="n">
-        <v>28907</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B340" s="13" t="n">
-        <v>17478</v>
-      </c>
-      <c r="C340" s="13" t="n">
-        <v>16266</v>
+        <v>-3600</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B341" s="13">
-        <f>B339-B340</f>
-        <v/>
-      </c>
-      <c r="C341" s="13">
-        <f>C339-C340</f>
-        <v/>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B341" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B342" s="16">
-        <f>B341/B339</f>
-        <v/>
-      </c>
-      <c r="C342" s="16">
-        <f>C341/C339</f>
-        <v/>
-      </c>
-    </row>
-    <row r="343"/>
-    <row r="344"/>
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B342" s="17" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B343" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B344" s="13">
+        <f>-B342*B343</f>
+        <v/>
+      </c>
+    </row>
     <row r="345">
-      <c r="A345" s="5" t="inlineStr">
-        <is>
-          <t>Call-out revenue, September</t>
-        </is>
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B345" s="13">
+        <f>B339+B340+B341+B344</f>
+        <v/>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="12" t="inlineStr">
-        <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
-        </is>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" s="6" t="inlineStr"/>
-      <c r="B347" s="7" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B348" s="13" t="n">
-        <v>21543</v>
-      </c>
-    </row>
+      <c r="A346" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B346" s="16">
+        <f>B345/B339</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347"/>
+    <row r="348"/>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B349" s="13" t="n">
-        <v>7380</v>
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t>Milton office LED lighting</t>
+        </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Mark-up on materials</t>
-        </is>
-      </c>
-      <c r="B350" s="14" t="n">
-        <v>0.3</v>
+      <c r="A350" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B351" s="13">
-        <f>B349*(1+B350)</f>
-        <v/>
+      <c r="A351" s="6" t="inlineStr"/>
+      <c r="B351" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Materials charged (as invoiced, rounded per call-out)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B352" s="13" t="n">
-        <v>9594</v>
+        <v>18600</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Call-out revenue</t>
-        </is>
-      </c>
-      <c r="B353" s="13">
-        <f>B348+B352</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B353" s="13" t="n">
+        <v>-6900</v>
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="15" t="inlineStr">
-        <is>
-          <t>Technician time, % of call-out revenue</t>
-        </is>
-      </c>
-      <c r="B354" s="16">
-        <f>B348/B353</f>
-        <v/>
-      </c>
-    </row>
-    <row r="355"/>
-    <row r="356"/>
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B354" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B355" s="17" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B356" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
     <row r="357">
-      <c r="A357" s="5" t="inlineStr">
-        <is>
-          <t>Call-out revenue, September</t>
-        </is>
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B357" s="13">
+        <f>-B355*B356</f>
+        <v/>
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="12" t="inlineStr">
-        <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
-        </is>
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B358" s="13">
+        <f>B352+B353+B354+B357</f>
+        <v/>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="6" t="inlineStr"/>
-      <c r="B359" s="7" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B360" s="13" t="n">
-        <v>21543</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B361" s="13" t="n">
-        <v>7380</v>
-      </c>
-    </row>
+      <c r="A359" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B359" s="16">
+        <f>B358/B352</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360"/>
+    <row r="361"/>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Mark-up on materials</t>
-        </is>
-      </c>
-      <c r="B362" s="14" t="n">
-        <v>0.3</v>
+      <c r="A362" s="5" t="inlineStr">
+        <is>
+          <t>Chermside clinic cabling</t>
+        </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B363" s="13">
-        <f>B361*(1+B362)</f>
-        <v/>
+      <c r="A363" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Materials charged (as invoiced, rounded per call-out)</t>
-        </is>
-      </c>
-      <c r="B364" s="13" t="n">
-        <v>9594</v>
+      <c r="A364" s="6" t="inlineStr"/>
+      <c r="B364" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Call-out revenue</t>
-        </is>
-      </c>
-      <c r="B365" s="13">
-        <f>B360+B364</f>
-        <v/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B365" s="13" t="n">
+        <v>15200</v>
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="15" t="inlineStr">
-        <is>
-          <t>Technician time, % of call-out revenue</t>
-        </is>
-      </c>
-      <c r="B366" s="16">
-        <f>B360/B365</f>
-        <v/>
-      </c>
-    </row>
-    <row r="367"/>
-    <row r="368"/>
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B366" s="13" t="n">
+        <v>-4300</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B367" s="13" t="n">
+        <v>-1800</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B368" s="17" t="n">
+        <v>52</v>
+      </c>
+    </row>
     <row r="369">
-      <c r="A369" s="5" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (6)</t>
-        </is>
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B369" s="13" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in September, added together</t>
-        </is>
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B370" s="13">
+        <f>-B368*B369</f>
+        <v/>
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="6" t="inlineStr"/>
-      <c r="B371" s="7" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B371" s="13">
+        <f>B365+B366+B367+B370</f>
+        <v/>
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B372" s="13" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B373" s="13" t="n">
-        <v>870</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B374" s="13" t="n">
-        <v>923</v>
-      </c>
-    </row>
+      <c r="A372" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B372" s="16">
+        <f>B371/B365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373"/>
+    <row r="374"/>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B375" s="13">
-        <f>B373+B374</f>
-        <v/>
+      <c r="A375" s="5" t="inlineStr">
+        <is>
+          <t>West End cafe air-con</t>
+        </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B376" s="13" t="n">
-        <v>-710</v>
+      <c r="A376" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B377" s="13" t="n">
-        <v>-408</v>
+      <c r="A377" s="6" t="inlineStr"/>
+      <c r="B377" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B378" s="13" t="n">
+        <v>12900</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B379" s="13" t="n">
+        <v>-5100</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B380" s="13" t="n">
+        <v>-900</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B381" s="17" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B382" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B383" s="13">
+        <f>-B381*B382</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B378" s="13">
-        <f>B375+B376+B377</f>
-        <v/>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="15" t="inlineStr">
+      <c r="B384" s="13">
+        <f>B378+B379+B380+B383</f>
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B379" s="16">
-        <f>B378/B375</f>
-        <v/>
-      </c>
-    </row>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382">
-      <c r="A382" s="5" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (13)</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in September, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="6" t="inlineStr"/>
-      <c r="B384" s="7" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B385" s="13" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B386" s="13" t="n">
-        <v>2834</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B387" s="13" t="n">
-        <v>1833</v>
-      </c>
-    </row>
+      <c r="B385" s="16">
+        <f>B384/B378</f>
+        <v/>
+      </c>
+    </row>
+    <row r="386"/>
+    <row r="387"/>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B388" s="13">
-        <f>B386+B387</f>
-        <v/>
+      <c r="A388" s="5" t="inlineStr">
+        <is>
+          <t>Carindale solar and battery</t>
+        </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B389" s="13" t="n">
-        <v>-1410</v>
+      <c r="A389" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B390" s="13" t="n">
-        <v>-1326</v>
+      <c r="A390" s="6" t="inlineStr"/>
+      <c r="B390" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B391" s="13" t="n">
+        <v>27400</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B392" s="13" t="n">
+        <v>-13800</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B393" s="13" t="n">
+        <v>-3100</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B394" s="17" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B395" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B396" s="13">
+        <f>-B394*B395</f>
+        <v/>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B391" s="13">
-        <f>B388+B389+B390</f>
-        <v/>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" s="15" t="inlineStr">
+      <c r="B397" s="13">
+        <f>B391+B392+B393+B396</f>
+        <v/>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B392" s="16">
-        <f>B391/B388</f>
-        <v/>
-      </c>
-    </row>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395">
-      <c r="A395" s="5" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (17)</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in September, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" s="6" t="inlineStr"/>
-      <c r="B397" s="7" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B398" s="13" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B399" s="13" t="n">
-        <v>4930</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B400" s="13" t="n">
-        <v>2860</v>
-      </c>
-    </row>
+      <c r="B398" s="16">
+        <f>B397/B391</f>
+        <v/>
+      </c>
+    </row>
+    <row r="399"/>
+    <row r="400"/>
     <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B401" s="13">
-        <f>B399+B400</f>
-        <v/>
+      <c r="A401" s="5" t="inlineStr">
+        <is>
+          <t>Wacol warehouse switchboard</t>
+        </is>
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B402" s="13" t="n">
-        <v>-2200</v>
+      <c r="A402" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B403" s="13" t="n">
-        <v>-2312</v>
+      <c r="A403" s="6" t="inlineStr"/>
+      <c r="B403" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B404" s="13" t="n">
+        <v>46800</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B405" s="13" t="n">
+        <v>-22900</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B406" s="13" t="n">
+        <v>-7400</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B407" s="17" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B408" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B409" s="13">
+        <f>-B407*B408</f>
+        <v/>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B404" s="13">
-        <f>B401+B402+B403</f>
-        <v/>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="15" t="inlineStr">
+      <c r="B410" s="13">
+        <f>B404+B405+B406+B409</f>
+        <v/>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B405" s="16">
-        <f>B404/B401</f>
-        <v/>
-      </c>
-    </row>
-    <row r="406"/>
-    <row r="407"/>
-    <row r="408">
-      <c r="A408" s="5" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in September, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" s="6" t="inlineStr"/>
-      <c r="B410" s="7" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B411" s="13" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B412" s="13" t="n">
-        <v>2904</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B413" s="13" t="n">
-        <v>1092</v>
-      </c>
-    </row>
+      <c r="B411" s="16">
+        <f>B410/B404</f>
+        <v/>
+      </c>
+    </row>
+    <row r="412"/>
+    <row r="413"/>
     <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B414" s="13">
-        <f>B412+B413</f>
-        <v/>
+      <c r="A414" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs: gross margin, September and August</t>
+        </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B415" s="13" t="n">
-        <v>-840</v>
+      <c r="A415" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B416" s="13" t="n">
-        <v>-1360</v>
+      <c r="A416" s="6" t="inlineStr"/>
+      <c r="B416" s="7" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="C416" s="7" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B417" s="13">
-        <f>B414+B415+B416</f>
-        <v/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B417" s="13" t="n">
+        <v>31137</v>
+      </c>
+      <c r="C417" s="13" t="n">
+        <v>28907</v>
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B418" s="16">
-        <f>B417/B414</f>
-        <v/>
-      </c>
-    </row>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421">
-      <c r="A421" s="5" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in September, added together</t>
-        </is>
-      </c>
-    </row>
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B418" s="13" t="n">
+        <v>17478</v>
+      </c>
+      <c r="C418" s="13" t="n">
+        <v>16266</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B419" s="13">
+        <f>B417-B418</f>
+        <v/>
+      </c>
+      <c r="C419" s="13">
+        <f>C417-C418</f>
+        <v/>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B420" s="16">
+        <f>B419/B417</f>
+        <v/>
+      </c>
+      <c r="C420" s="16">
+        <f>C419/C417</f>
+        <v/>
+      </c>
+    </row>
+    <row r="421"/>
+    <row r="422"/>
     <row r="423">
-      <c r="A423" s="6" t="inlineStr"/>
-      <c r="B423" s="7" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
+      <c r="A423" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs: gross margin, September and August</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B424" s="13" t="n">
-        <v>11</v>
+      <c r="A424" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B425" s="13" t="n">
-        <v>4785</v>
+      <c r="A425" s="6" t="inlineStr"/>
+      <c r="B425" s="7" t="inlineStr">
+        <is>
+          <t>Sep 26</t>
+        </is>
+      </c>
+      <c r="C425" s="7" t="inlineStr">
+        <is>
+          <t>Aug 26</t>
+        </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B426" s="13" t="n">
-        <v>1573</v>
+        <v>31137</v>
+      </c>
+      <c r="C426" s="13" t="n">
+        <v>28907</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B427" s="13">
-        <f>B425+B426</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B427" s="13" t="n">
+        <v>17478</v>
+      </c>
+      <c r="C427" s="13" t="n">
+        <v>16266</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B428" s="13" t="n">
-        <v>-1210</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B428" s="13">
+        <f>B426-B427</f>
+        <v/>
+      </c>
+      <c r="C428" s="13">
+        <f>C426-C427</f>
+        <v/>
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B429" s="13" t="n">
-        <v>-2244</v>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B430" s="13">
-        <f>B427+B428+B429</f>
-        <v/>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B431" s="16">
-        <f>B430/B427</f>
-        <v/>
-      </c>
-    </row>
-    <row r="432"/>
-    <row r="433"/>
+      <c r="A429" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B429" s="16">
+        <f>B428/B426</f>
+        <v/>
+      </c>
+      <c r="C429" s="16">
+        <f>C428/C426</f>
+        <v/>
+      </c>
+    </row>
+    <row r="430"/>
+    <row r="431"/>
+    <row r="432">
+      <c r="A432" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
     <row r="434">
-      <c r="A434" s="5" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (9)</t>
+      <c r="A434" s="6" t="inlineStr"/>
+      <c r="B434" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
         </is>
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in September, added together</t>
-        </is>
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B435" s="13" t="n">
+        <v>73107</v>
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="6" t="inlineStr"/>
-      <c r="B436" s="7" t="inlineStr">
-        <is>
-          <t>Sep 2026</t>
-        </is>
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B436" s="13" t="n">
+        <v>54600</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
       <c r="B437" s="13" t="n">
-        <v>9</v>
+        <v>51170</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B438" s="13" t="n">
-        <v>5220</v>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B438" s="13">
+        <f>B436-B437</f>
+        <v/>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B439" s="13" t="n">
-        <v>1313</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B439" s="13">
+        <f>B435-B438</f>
+        <v/>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B440" s="13">
-        <f>B438+B439</f>
-        <v/>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B440" s="13" t="n">
+        <v>59580</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B441" s="13" t="n">
-        <v>-1010</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B441" s="13">
+        <f>B439-B440</f>
+        <v/>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B442" s="13" t="n">
-        <v>-2448</v>
+        <v>202337</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B443" s="14">
+        <f>B435/B442</f>
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B444" s="14">
+        <f>B441/B442</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B445" s="16">
+        <f>(B438+B440)/B442</f>
+        <v/>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447"/>
+    <row r="448"/>
+    <row r="449">
+      <c r="A449" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, September</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="6" t="inlineStr"/>
+      <c r="B451" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B452" s="13" t="n">
+        <v>21543</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B453" s="13" t="n">
+        <v>7380</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B454" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B455" s="13">
+        <f>B453*(1+B454)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B456" s="13" t="n">
+        <v>9594</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B457" s="13">
+        <f>B452+B456</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B458" s="16">
+        <f>B452/B457</f>
+        <v/>
+      </c>
+    </row>
+    <row r="459"/>
+    <row r="460"/>
+    <row r="461">
+      <c r="A461" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, September</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="6" t="inlineStr"/>
+      <c r="B463" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B464" s="13" t="n">
+        <v>21543</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B465" s="13" t="n">
+        <v>7380</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B466" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B467" s="13">
+        <f>B465*(1+B466)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B468" s="13" t="n">
+        <v>9594</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B469" s="13">
+        <f>B464+B468</f>
+        <v/>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B470" s="16">
+        <f>B464/B469</f>
+        <v/>
+      </c>
+    </row>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473">
+      <c r="A473" s="5" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in September, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="6" t="inlineStr"/>
+      <c r="B475" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B476" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B477" s="13" t="n">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B478" s="13" t="n">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B479" s="13">
+        <f>B477+B478</f>
+        <v/>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B480" s="13" t="n">
+        <v>-710</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B481" s="13" t="n">
+        <v>-408</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B443" s="13">
-        <f>B440+B441+B442</f>
-        <v/>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" s="15" t="inlineStr">
+      <c r="B482" s="13">
+        <f>B479+B480+B481</f>
+        <v/>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B444" s="16">
-        <f>B443/B440</f>
-        <v/>
-      </c>
-    </row>
-    <row r="445"/>
-    <row r="446"/>
-    <row r="447"/>
+      <c r="B483" s="16">
+        <f>B482/B479</f>
+        <v/>
+      </c>
+    </row>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486">
+      <c r="A486" s="5" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in September, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="6" t="inlineStr"/>
+      <c r="B488" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B489" s="13" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B490" s="13" t="n">
+        <v>2834</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B491" s="13" t="n">
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B492" s="13">
+        <f>B490+B491</f>
+        <v/>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B493" s="13" t="n">
+        <v>-1410</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B494" s="13" t="n">
+        <v>-1326</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B495" s="13">
+        <f>B492+B493+B494</f>
+        <v/>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B496" s="16">
+        <f>B495/B492</f>
+        <v/>
+      </c>
+    </row>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499">
+      <c r="A499" s="5" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in September, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="6" t="inlineStr"/>
+      <c r="B501" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B502" s="13" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B503" s="13" t="n">
+        <v>4930</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B504" s="13" t="n">
+        <v>2860</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B505" s="13">
+        <f>B503+B504</f>
+        <v/>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B506" s="13" t="n">
+        <v>-2200</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B507" s="13" t="n">
+        <v>-2312</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B508" s="13">
+        <f>B505+B506+B507</f>
+        <v/>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B509" s="16">
+        <f>B508/B505</f>
+        <v/>
+      </c>
+    </row>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512">
+      <c r="A512" s="5" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in September, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="6" t="inlineStr"/>
+      <c r="B514" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B515" s="13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B516" s="13" t="n">
+        <v>2904</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B517" s="13" t="n">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B518" s="13">
+        <f>B516+B517</f>
+        <v/>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B519" s="13" t="n">
+        <v>-840</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B520" s="13" t="n">
+        <v>-1360</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B521" s="13">
+        <f>B518+B519+B520</f>
+        <v/>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B522" s="16">
+        <f>B521/B518</f>
+        <v/>
+      </c>
+    </row>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525">
+      <c r="A525" s="5" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in September, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="6" t="inlineStr"/>
+      <c r="B527" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B528" s="13" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B529" s="13" t="n">
+        <v>4785</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B530" s="13" t="n">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B531" s="13">
+        <f>B529+B530</f>
+        <v/>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B532" s="13" t="n">
+        <v>-1210</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B533" s="13" t="n">
+        <v>-2244</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B534" s="13">
+        <f>B531+B532+B533</f>
+        <v/>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B535" s="16">
+        <f>B534/B531</f>
+        <v/>
+      </c>
+    </row>
+    <row r="536"/>
+    <row r="537"/>
+    <row r="538">
+      <c r="A538" s="5" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in September, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="6" t="inlineStr"/>
+      <c r="B540" s="7" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B541" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B542" s="13" t="n">
+        <v>5220</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B543" s="13" t="n">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B544" s="13">
+        <f>B542+B543</f>
+        <v/>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B545" s="13" t="n">
+        <v>-1010</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B546" s="13" t="n">
+        <v>-2448</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B547" s="13">
+        <f>B544+B545+B546</f>
+        <v/>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B548" s="16">
+        <f>B547/B544</f>
+        <v/>
+      </c>
+    </row>
+    <row r="549"/>
+    <row r="550"/>
+    <row r="551"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -5174,24 +6231,27 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="17" manualBreakCount="17">
+  <rowBreaks count="20" manualBreakCount="20">
     <brk id="30" min="0" max="16383" man="1"/>
-    <brk id="57" min="0" max="16383" man="1"/>
-    <brk id="79" min="0" max="16383" man="1"/>
-    <brk id="105" min="0" max="16383" man="1"/>
+    <brk id="56" min="0" max="16383" man="1"/>
+    <brk id="83" min="0" max="16383" man="1"/>
+    <brk id="101" min="0" max="16383" man="1"/>
     <brk id="131" min="0" max="16383" man="1"/>
     <brk id="157" min="0" max="16383" man="1"/>
     <brk id="183" min="0" max="16383" man="1"/>
     <brk id="209" min="0" max="16383" man="1"/>
     <brk id="235" min="0" max="16383" man="1"/>
-    <brk id="257" min="0" max="16383" man="1"/>
-    <brk id="283" min="0" max="16383" man="1"/>
-    <brk id="309" min="0" max="16383" man="1"/>
-    <brk id="335" min="0" max="16383" man="1"/>
-    <brk id="356" min="0" max="16383" man="1"/>
-    <brk id="381" min="0" max="16383" man="1"/>
-    <brk id="407" min="0" max="16383" man="1"/>
-    <brk id="433" min="0" max="16383" man="1"/>
+    <brk id="261" min="0" max="16383" man="1"/>
+    <brk id="287" min="0" max="16383" man="1"/>
+    <brk id="318" min="0" max="16383" man="1"/>
+    <brk id="348" min="0" max="16383" man="1"/>
+    <brk id="374" min="0" max="16383" man="1"/>
+    <brk id="400" min="0" max="16383" man="1"/>
+    <brk id="431" min="0" max="16383" man="1"/>
+    <brk id="460" min="0" max="16383" man="1"/>
+    <brk id="485" min="0" max="16383" man="1"/>
+    <brk id="511" min="0" max="16383" man="1"/>
+    <brk id="537" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/media/exports/reports/2026-09/job-margins.xlsx
+++ b/media/exports/reports/2026-09/job-margins.xlsx
@@ -12,7 +12,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="Job_gross_margin_September_All_jobs">'Report'!$B$15</definedName>
+    <definedName name="Job_gross_margin_August_All_jobs">'Report'!$B$16</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$17</definedName>
+    <definedName name="Job_gross_margin_September_Maintenance_contracts">'Report'!$B$41</definedName>
+    <definedName name="Job_gross_margin_August_Maintenance_contracts">'Report'!$B$42</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$43</definedName>
+    <definedName name="Job_gross_margin_September_Installations">'Report'!$B$80</definedName>
+    <definedName name="Job_gross_margin_August_Installations">'Report'!$B$81</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$82</definedName>
+    <definedName name="Job_gross_margin_September_Call_outs_and_repairs">'Report'!$B$108</definedName>
+    <definedName name="Job_gross_margin_August_Call_outs_and_repairs">'Report'!$B$109</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$110</definedName>
+    <definedName name="Technician_time_charged_September">'Report'!$B$111</definedName>
+    <definedName name="Materials_charged_September">'Report'!$B$112</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$137</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$548</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,11 +67,6 @@
       <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
@@ -70,6 +82,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="002F7A5D"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -118,27 +135,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,6 +238,834 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin by type of job, September 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$21:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$21:$B$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on each maintenance contract, September 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$47:$A$60</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$47:$B$60</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on each installation invoiced in September 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$86:$A$91</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$86:$B$91</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on call-outs by length, September 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$116:$A$121</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$116:$B$121</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Revenue by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>All</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$6:$D$29</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Maintenance contracts</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2F7A5D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$30:$D$53</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Installations</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="8A6D3B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$54:$D$77</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Call-outs and repairs</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5F6F63"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$78:$D$101</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="2"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="4500000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>84</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>114</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="job_margins_Data" displayName="job_margins_Data" ref="A5:G101" headerRowCount="1">
+  <autoFilter ref="A5:G101"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Revenue"/>
+    <tableColumn id="5" name="Direct cost"/>
+    <tableColumn id="6" name="Gross margin"/>
+    <tableColumn id="7" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -510,7 +1357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D107"/>
+  <dimension ref="A1:D139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -529,14 +1376,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -552,14 +1399,14 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Gross margin, not profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>From gross margin to profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>September's jobs made $73,107 gross margin (36.1%). Technician time not charged to jobs took $3,430 and overheads $59,580, leaving $10,097 profit before tax (5.0% of revenue). To cover overheads, jobs need a 31.1% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -567,14 +1414,14 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>From gross margin to profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
+          <t>Gross margin, not profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>September's jobs made $73,107 gross margin (36.1%). Technician time not charged to jobs took $3,430 and overheads $59,580, leaving $10,097 profit before tax (5.0% of revenue). To cover overheads, jobs need a 31.1% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
         </is>
       </c>
     </row>
@@ -718,858 +1565,890 @@
       </c>
     </row>
     <row r="24"/>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>In September maintenance contracts made a 59.5% job gross margin, installations made a 27.0% job gross margin, call-outs and repairs made a 43.9% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 31.1% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="60" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Installations: 27.0% gross margin, 8.0 points under the 35.0% target: about $10,413 on $130,700 of revenue in September. It's below the 31.1% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in September).</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Type of job: Maintenance contracts</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Job gross margin, September · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B33" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Job gross margin, August · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B34" s="8">
-        <f>Workings!B99</f>
-        <v/>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B35" s="8">
-        <f>Workings!B115</f>
-        <v/>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (September)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each maintenance contract, September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr"/>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Carindale vet clinic</t>
-        </is>
-      </c>
-      <c r="B39" s="8">
-        <f>Workings!B129</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>Workings!B128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B40" s="8">
-        <f>Workings!B142</f>
-        <v/>
-      </c>
-      <c r="C40" s="11">
-        <f>Workings!B141</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Job gross margin, September · Maintenance contracts</t>
         </is>
       </c>
       <c r="B41" s="8">
-        <f>Workings!B155</f>
-        <v/>
-      </c>
-      <c r="C41" s="11">
-        <f>Workings!B154</f>
-        <v/>
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Job gross margin, August · Maintenance contracts</t>
         </is>
       </c>
       <c r="B42" s="8">
-        <f>Workings!B168</f>
-        <v/>
-      </c>
-      <c r="C42" s="11">
-        <f>Workings!B167</f>
-        <v/>
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B43" s="8">
-        <f>Workings!B181</f>
-        <v/>
-      </c>
-      <c r="C43" s="11">
-        <f>Workings!B180</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Riverside Apartments (strata)</t>
-        </is>
-      </c>
-      <c r="B44" s="8">
-        <f>Workings!B194</f>
-        <v/>
-      </c>
-      <c r="C44" s="11">
-        <f>Workings!B193</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B115</f>
+        <v/>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (September)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Newstead gym</t>
-        </is>
-      </c>
-      <c r="B45" s="8">
-        <f>Workings!B207</f>
-        <v/>
-      </c>
-      <c r="C45" s="11">
-        <f>Workings!B206</f>
-        <v/>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each maintenance contract, September 2026</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Chermside retail centre</t>
-        </is>
-      </c>
-      <c r="B46" s="8">
-        <f>Workings!B220</f>
-        <v/>
-      </c>
-      <c r="C46" s="11">
-        <f>Workings!B219</f>
-        <v/>
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
+          <t>Carindale vet clinic</t>
         </is>
       </c>
       <c r="B47" s="8">
-        <f>Workings!B233</f>
+        <f>Workings!B129</f>
         <v/>
       </c>
       <c r="C47" s="11">
-        <f>Workings!B232</f>
+        <f>Workings!B128</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
       <c r="B48" s="8">
-        <f>Workings!B246</f>
+        <f>Workings!B142</f>
         <v/>
       </c>
       <c r="C48" s="11">
-        <f>Workings!B245</f>
+        <f>Workings!B141</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B49" s="8">
-        <f>Workings!B259</f>
+        <f>Workings!B155</f>
         <v/>
       </c>
       <c r="C49" s="11">
-        <f>Workings!B258</f>
+        <f>Workings!B154</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B50" s="8">
-        <f>Workings!B272</f>
+        <f>Workings!B168</f>
         <v/>
       </c>
       <c r="C50" s="11">
-        <f>Workings!B271</f>
+        <f>Workings!B167</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B51" s="8">
-        <f>Workings!B285</f>
+        <f>Workings!B181</f>
         <v/>
       </c>
       <c r="C51" s="11">
-        <f>Workings!B284</f>
+        <f>Workings!B180</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Riverside Apartments (strata)</t>
+        </is>
+      </c>
+      <c r="B52" s="8">
+        <f>Workings!B194</f>
+        <v/>
+      </c>
+      <c r="C52" s="11">
+        <f>Workings!B193</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Newstead gym</t>
+        </is>
+      </c>
+      <c r="B53" s="8">
+        <f>Workings!B207</f>
+        <v/>
+      </c>
+      <c r="C53" s="11">
+        <f>Workings!B206</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chermside retail centre</t>
+        </is>
+      </c>
+      <c r="B54" s="8">
+        <f>Workings!B220</f>
+        <v/>
+      </c>
+      <c r="C54" s="11">
+        <f>Workings!B219</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Wacol logistics depot</t>
+        </is>
+      </c>
+      <c r="B55" s="8">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C55" s="11">
+        <f>Workings!B232</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Milton office tower</t>
+        </is>
+      </c>
+      <c r="B56" s="8">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C56" s="11">
+        <f>Workings!B245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B57" s="8">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C57" s="11">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B58" s="8">
+        <f>Workings!B272</f>
+        <v/>
+      </c>
+      <c r="C58" s="11">
+        <f>Workings!B271</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B59" s="8">
+        <f>Workings!B285</f>
+        <v/>
+      </c>
+      <c r="C59" s="11">
+        <f>Workings!B284</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B52" s="8">
+      <c r="B60" s="8">
         <f>Workings!B298</f>
         <v/>
       </c>
-      <c r="C52" s="11">
+      <c r="C60" s="11">
         <f>Workings!B297</f>
         <v/>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>All 14 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
         </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in September). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in September).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C61" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Job gross margin, September · Installations</t>
-        </is>
-      </c>
-      <c r="B62" s="8">
-        <f>Workings!B307</f>
-        <v/>
-      </c>
-      <c r="C62" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Job gross margin, August · Installations</t>
-        </is>
-      </c>
-      <c r="B63" s="8">
-        <f>Workings!B316</f>
-        <v/>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B64" s="8">
-        <f>Workings!B332</f>
-        <v/>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (September)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each installation invoiced in September 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr"/>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Bulimba EV chargers</t>
-        </is>
-      </c>
-      <c r="B68" s="8">
-        <f>Workings!B346</f>
-        <v/>
-      </c>
-      <c r="C68" s="11">
-        <f>Workings!B345</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Milton office LED lighting</t>
-        </is>
-      </c>
-      <c r="B69" s="8">
-        <f>Workings!B359</f>
-        <v/>
-      </c>
-      <c r="C69" s="11">
-        <f>Workings!B358</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Chermside clinic cabling</t>
-        </is>
-      </c>
-      <c r="B70" s="8">
-        <f>Workings!B372</f>
-        <v/>
-      </c>
-      <c r="C70" s="11">
-        <f>Workings!B371</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>West End cafe air-con</t>
-        </is>
-      </c>
-      <c r="B71" s="8">
-        <f>Workings!B385</f>
-        <v/>
-      </c>
-      <c r="C71" s="11">
-        <f>Workings!B384</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Carindale solar and battery</t>
-        </is>
-      </c>
-      <c r="B72" s="8">
-        <f>Workings!B398</f>
-        <v/>
-      </c>
-      <c r="C72" s="11">
-        <f>Workings!B397</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Wacol warehouse switchboard</t>
-        </is>
-      </c>
-      <c r="B73" s="8">
-        <f>Workings!B411</f>
-        <v/>
-      </c>
-      <c r="C73" s="11">
-        <f>Workings!B410</f>
-        <v/>
       </c>
     </row>
     <row r="74"/>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="60" customHeight="1">
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>3 of the 6 installation jobs invoiced in September made less than the 35.0% job gross margin target. The Wacol warehouse switchboard made a 13.5% job gross margin: 150.0 h of technician time ($10,200) and $7,400 of subcontractors on a $46,800 job. Jobs need 31.1% gross margin just to cover overheads.</t>
+          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in September). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in September).</t>
         </is>
       </c>
     </row>
     <row r="77"/>
     <row r="78">
-      <c r="A78" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="60" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>3 installations under the 35.0% target, worth about $12,497 between them on $87,100 of revenue. The biggest gap, Wacol warehouse switchboard: 13.5% gross margin, 21.5 points under the 35.0% target: about $10,080 on $46,800 of revenue in September. It's below the 31.1% needed to cover overheads, too.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80"/>
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Installations</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>Compared with</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Job gross margin, September · Installations</t>
+        </is>
+      </c>
+      <c r="B80" s="8">
+        <f>Workings!B307</f>
+        <v/>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="81">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Job gross margin, August · Installations</t>
+        </is>
+      </c>
+      <c r="B81" s="8">
+        <f>Workings!B316</f>
+        <v/>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C82" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Job gross margin, September · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B83" s="8">
-        <f>Workings!B420</f>
-        <v/>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B82" s="8">
+        <f>Workings!B332</f>
+        <v/>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (September)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83"/>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Job gross margin, August · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B84" s="8">
-        <f>Workings!B429</f>
-        <v/>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each installation invoiced in September 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B85" s="8">
-        <f>Workings!B445</f>
-        <v/>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (September)</t>
+      <c r="A85" s="6" t="inlineStr"/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Technician time charged, September</t>
+          <t>Bulimba EV chargers</t>
         </is>
       </c>
       <c r="B86" s="8">
-        <f>Workings!B458</f>
-        <v/>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>69.2% of call-out revenue</t>
-        </is>
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C86" s="11">
+        <f>Workings!B345</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Materials charged, September</t>
+          <t>Milton office LED lighting</t>
         </is>
       </c>
       <c r="B87" s="8">
-        <f>Workings!B470</f>
-        <v/>
-      </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>$7,380 at cost, plus 30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="88"/>
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C87" s="11">
+        <f>Workings!B358</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Chermside clinic cabling</t>
+        </is>
+      </c>
+      <c r="B88" s="8">
+        <f>Workings!B372</f>
+        <v/>
+      </c>
+      <c r="C88" s="11">
+        <f>Workings!B371</f>
+        <v/>
+      </c>
+    </row>
     <row r="89">
-      <c r="A89" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on call-outs by length, September 2026</t>
-        </is>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>West End cafe air-con</t>
+        </is>
+      </c>
+      <c r="B89" s="8">
+        <f>Workings!B385</f>
+        <v/>
+      </c>
+      <c r="C89" s="11">
+        <f>Workings!B384</f>
+        <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="6" t="inlineStr"/>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C90" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Carindale solar and battery</t>
+        </is>
+      </c>
+      <c r="B90" s="8">
+        <f>Workings!B398</f>
+        <v/>
+      </c>
+      <c r="C90" s="11">
+        <f>Workings!B397</f>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>Wacol warehouse switchboard</t>
+        </is>
+      </c>
+      <c r="B91" s="8">
+        <f>Workings!B411</f>
+        <v/>
+      </c>
+      <c r="C91" s="11">
+        <f>Workings!B410</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98"/>
+    <row r="99"/>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="60" customHeight="1">
+      <c r="A101" s="3" t="inlineStr">
+        <is>
+          <t>3 of the 6 installation jobs invoiced in September made less than the 35.0% job gross margin target. The Wacol warehouse switchboard made a 13.5% job gross margin: 150.0 h of technician time ($10,200) and $7,400 of subcontractors on a $46,800 job. Jobs need 31.1% gross margin just to cover overheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102"/>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="60" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>3 installations under the 35.0% target, worth about $12,497 between them on $87,100 of revenue. The biggest gap, Wacol warehouse switchboard: 13.5% gross margin, 21.5 points under the 35.0% target: about $10,080 on $46,800 of revenue in September. It's below the 31.1% needed to cover overheads, too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105"/>
+    <row r="106">
+      <c r="A106" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Call-outs and repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C107" s="7" t="inlineStr">
+        <is>
+          <t>Compared with</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Job gross margin, September · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B108" s="8">
+        <f>Workings!B420</f>
+        <v/>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Job gross margin, August · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B109" s="8">
+        <f>Workings!B429</f>
+        <v/>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B110" s="8">
+        <f>Workings!B445</f>
+        <v/>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (September)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Technician time charged, September</t>
+        </is>
+      </c>
+      <c r="B111" s="8">
+        <f>Workings!B458</f>
+        <v/>
+      </c>
+      <c r="C111" s="9" t="inlineStr">
+        <is>
+          <t>69.2% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Materials charged, September</t>
+        </is>
+      </c>
+      <c r="B112" s="8">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C112" s="9" t="inlineStr">
+        <is>
+          <t>$7,380 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="113"/>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on call-outs by length, September 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr"/>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C115" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
           <t>1-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B91" s="8">
+      <c r="B116" s="8">
         <f>Workings!B483</f>
         <v/>
       </c>
-      <c r="C91" s="11">
+      <c r="C116" s="11">
         <f>Workings!B482</f>
         <v/>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>1.5-hour call-outs (13)</t>
         </is>
       </c>
-      <c r="B92" s="8">
+      <c r="B117" s="8">
         <f>Workings!B496</f>
         <v/>
       </c>
-      <c r="C92" s="11">
+      <c r="C117" s="11">
         <f>Workings!B495</f>
         <v/>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>2-hour call-outs (17)</t>
         </is>
       </c>
-      <c r="B93" s="8">
+      <c r="B118" s="8">
         <f>Workings!B509</f>
         <v/>
       </c>
-      <c r="C93" s="11">
+      <c r="C118" s="11">
         <f>Workings!B508</f>
         <v/>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>2.5-hour call-outs (8)</t>
         </is>
       </c>
-      <c r="B94" s="8">
+      <c r="B119" s="8">
         <f>Workings!B522</f>
         <v/>
       </c>
-      <c r="C94" s="11">
+      <c r="C119" s="11">
         <f>Workings!B521</f>
         <v/>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>3-hour call-outs (11)</t>
         </is>
       </c>
-      <c r="B95" s="8">
+      <c r="B120" s="8">
         <f>Workings!B535</f>
         <v/>
       </c>
-      <c r="C95" s="11">
+      <c r="C120" s="11">
         <f>Workings!B534</f>
         <v/>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>4-hour call-outs (9)</t>
         </is>
       </c>
-      <c r="B96" s="8">
+      <c r="B121" s="8">
         <f>Workings!B548</f>
         <v/>
       </c>
-      <c r="C96" s="11">
+      <c r="C121" s="11">
         <f>Workings!B547</f>
         <v/>
       </c>
     </row>
-    <row r="97"/>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
+    <row r="129"/>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
+    <row r="131" ht="60" customHeight="1">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>64 call-outs in September billed $21,543 of technician time and $9,594 of materials ($7,380 at cost plus 30%), and made a 43.9% job gross margin between them. Gross margins run from 37.6% to 47.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="132"/>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="3" t="inlineStr">
+    <row r="134" ht="30" customHeight="1">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>All call-outs: 43.9% gross margin, 8.9 points over the 35.0% target ($2,761 ahead on $31,137 in September).</t>
         </is>
       </c>
     </row>
-    <row r="103"/>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
+    <row r="135"/>
+    <row r="136">
+      <c r="A136" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="12" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="106"/>
-    <row r="107"/>
+    <row r="138"/>
+    <row r="139"/>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A102:D102"/>
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A101:D101"/>
+    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="A134:D134"/>
+    <mergeCell ref="A73:D73"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A99:D99"/>
     <mergeCell ref="A76:D76"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -1577,18 +2456,20 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="4" manualBreakCount="4">
+  <rowBreaks count="5" manualBreakCount="5">
     <brk id="18" min="0" max="16383" man="1"/>
-    <brk id="36" min="0" max="16383" man="1"/>
-    <brk id="65" min="0" max="16383" man="1"/>
-    <brk id="88" min="0" max="16383" man="1"/>
+    <brk id="44" min="0" max="16383" man="1"/>
+    <brk id="71" min="0" max="16383" man="1"/>
+    <brk id="99" min="0" max="16383" man="1"/>
+    <brk id="113" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1617,14 +2498,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1632,7 +2513,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, September 2026</t>
+          <t>Trades: From gross margin to profit, September 2026</t>
         </is>
       </c>
     </row>
@@ -1779,7 +2660,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>All lines: gross margin, September and August</t>
+          <t>Trades, all lines: gross margin, September and August</t>
         </is>
       </c>
     </row>
@@ -1864,7 +2745,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>All lines: gross margin, September and August</t>
+          <t>Trades, all lines: gross margin, September and August</t>
         </is>
       </c>
     </row>
@@ -1949,7 +2830,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, September 2026</t>
+          <t>Trades: From gross margin to profit, September 2026</t>
         </is>
       </c>
     </row>
@@ -2294,7 +3175,7 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts: gross margin, September and August</t>
+          <t>Trades, Maintenance contracts: gross margin, September and August</t>
         </is>
       </c>
     </row>
@@ -2379,7 +3260,7 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts: gross margin, September and August</t>
+          <t>Trades, Maintenance contracts: gross margin, September and August</t>
         </is>
       </c>
     </row>
@@ -2464,7 +3345,7 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, September 2026</t>
+          <t>Trades: From gross margin to profit, September 2026</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4990,7 @@
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, September and August</t>
+          <t>Trades, Installations: gross margin, September and August</t>
         </is>
       </c>
     </row>
@@ -4194,7 +5075,7 @@
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, September and August</t>
+          <t>Trades, Installations: gross margin, September and August</t>
         </is>
       </c>
     </row>
@@ -4279,7 +5160,7 @@
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, September 2026</t>
+          <t>Trades: From gross margin to profit, September 2026</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5949,7 @@
     <row r="414">
       <c r="A414" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, September and August</t>
+          <t>Trades, Call-outs and repairs: gross margin, September and August</t>
         </is>
       </c>
     </row>
@@ -5153,7 +6034,7 @@
     <row r="423">
       <c r="A423" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, September and August</t>
+          <t>Trades, Call-outs and repairs: gross margin, September and August</t>
         </is>
       </c>
     </row>
@@ -5238,7 +6119,7 @@
     <row r="432">
       <c r="A432" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, September 2026</t>
+          <t>Trades: From gross margin to profit, September 2026</t>
         </is>
       </c>
     </row>
@@ -6225,7 +7106,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6284,14 +7165,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -9315,7 +10196,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -9326,5 +10207,9 @@
     <brk id="53" min="0" max="16383" man="1"/>
     <brk id="77" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-09/job-margins.xlsx
+++ b/media/exports/reports/2026-09/job-margins.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart lines" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Job_gross_margin_September_All_jobs">'Report'!$B$15</definedName>
@@ -28,8 +29,8 @@
     <definedName name="Materials_charged_September">'Report'!$B$112</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$137</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$548</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$101</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$G$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -264,7 +265,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin by type of job, September 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin by type of job, September 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -331,6 +332,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$4:$B$5</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$4:$C$5</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 31.1%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$8:$B$9</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$8:$C$9</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -346,6 +495,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.6842499999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -353,6 +504,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.6842499999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -385,7 +563,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each maintenance contract, September 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on each maintenance contract, September 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -438,6 +616,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$12:$B$13</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$12:$C$13</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 31.1%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$16:$B$17</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$16:$C$17</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -453,6 +779,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.7152999999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -460,6 +788,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.7152999999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -492,7 +847,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each installation invoiced in September 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on each installation invoiced in September 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -587,6 +942,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$20:$B$21</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$20:$C$21</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 31.1%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$24:$B$25</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$24:$C$25</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -602,6 +1105,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.5197999999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -609,6 +1114,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.5197999999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -641,7 +1173,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on call-outs by length, September 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on call-outs by length, September 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -694,6 +1226,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$28:$B$29</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$28:$C$29</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 31.1%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$32:$B$33</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$32:$C$33</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -709,6 +1389,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.54165"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -716,6 +1398,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.54165"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -941,7 +1650,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="1980000"/>
+    <ext cx="5400000" cy="2196000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -963,7 +1672,7 @@
       <row>45</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="4500000"/>
+    <ext cx="5400000" cy="4716000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -985,7 +1694,7 @@
       <row>84</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2340000"/>
+    <ext cx="5400000" cy="2556000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1007,7 +1716,7 @@
       <row>114</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2340000"/>
+    <ext cx="5400000" cy="2556000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1383,7 +2092,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -2456,7 +3165,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2505,7 +3214,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -7106,7 +7815,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7141,6 +7850,219 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Points for the target and break-even lines drawn on the charts (hidden sheet; edit the values on the chart's own sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin by type of job, September 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin by type of job, September 2026: Break-even 31.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each maintenance contract, September 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each maintenance contract, September 2026: Break-even 31.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each installation invoiced in September 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each installation invoiced in September 2026: Break-even 31.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on call-outs by length, September 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on call-outs by length, September 2026: Break-even 31.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G101"/>
@@ -7172,7 +8094,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -10196,7 +11118,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-09/job-margins.xlsx
+++ b/media/exports/reports/2026-09/job-margins.xlsx
@@ -409,7 +409,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 31.1%</v>
+            <v>Break-even 39.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -495,7 +495,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6842499999999999"/>
+          <max val="0.73485"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -509,7 +509,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6842499999999999"/>
+          <max val="0.73485"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -693,7 +693,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 31.1%</v>
+            <v>Break-even 39.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -779,7 +779,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7152999999999999"/>
+          <max val="0.7613"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -793,7 +793,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7152999999999999"/>
+          <max val="0.7613"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -877,20 +877,6 @@
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
-          <dPt>
-            <idx val="3"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dPt>
             <idx val="4"/>
             <spPr>
@@ -1019,7 +1005,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 31.1%</v>
+            <v>Break-even 39.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -1105,7 +1091,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.5197999999999999"/>
+          <max val="0.5888"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1119,7 +1105,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.5197999999999999"/>
+          <max val="0.5888"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1303,7 +1289,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 31.1%</v>
+            <v>Break-even 39.0%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -1389,7 +1375,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.54165"/>
+          <max val="0.5957"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1403,7 +1389,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.54165"/>
+          <max val="0.5957"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -2092,7 +2078,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2101,7 @@
     <row r="8" ht="60" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>September's jobs made $73,107 gross margin (36.1%). Technician time not charged to jobs took $3,430 and overheads $59,580, leaving $10,097 profit before tax (5.0% of revenue). To cover overheads, jobs need a 31.1% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>September's jobs made $96,230 gross margin (42.7%). Technician time not charged to jobs took $28,417 and overheads $59,580, leaving $8,233 profit before tax (3.7% of revenue). To cover overheads, jobs need a 39.0% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2116,7 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2278,7 @@
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>In September maintenance contracts made a 59.5% job gross margin, installations made a 27.0% job gross margin, call-outs and repairs made a 43.9% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 31.1% just to cover overheads.</t>
+          <t>In September maintenance contracts made a 63.9% job gross margin, installations made a 34.8% job gross margin, call-outs and repairs made a 48.3% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 39.0% just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2293,7 @@
     <row r="37" ht="60" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Installations: 27.0% gross margin, 8.0 points under the 35.0% target: about $10,413 on $130,700 of revenue in September. It's below the 31.1% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in September).</t>
+          <t>Installations: 34.8% gross margin, 0.2 points under the 35.0% target: about $273 on $146,300 of revenue in September. It's below the 39.0% needed to cover overheads, too. Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($13,094 ahead on $45,350 in September).</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2424,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B49" s="8">
@@ -2453,7 +2439,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
       <c r="B50" s="8">
@@ -2468,7 +2454,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B51" s="8">
@@ -2483,7 +2469,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B52" s="8">
@@ -2498,7 +2484,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B53" s="8">
@@ -2528,7 +2514,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
+          <t>Bulimba school</t>
         </is>
       </c>
       <c r="B55" s="8">
@@ -2543,7 +2529,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Wacol logistics depot</t>
         </is>
       </c>
       <c r="B56" s="8">
@@ -2558,7 +2544,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B57" s="8">
@@ -2636,7 +2622,7 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>All 14 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
+          <t>All 14 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 62.9% job gross margin: 14.0 h of technician time on a $2,700 monthly fee.</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2637,7 @@
     <row r="76" ht="45" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in September). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in September).</t>
+          <t>The thinnest, Kangaroo Point townhouses: 62.9% gross margin, 27.9 points over the 35.0% target ($753 ahead on $2,700 in September). All maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($13,094 ahead on $45,350 in September).</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2843,7 @@
     <row r="101" ht="60" customHeight="1">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>3 of the 6 installation jobs invoiced in September made less than the 35.0% job gross margin target. The Wacol warehouse switchboard made a 13.5% job gross margin: 150.0 h of technician time ($10,200) and $7,400 of subcontractors on a $46,800 job. Jobs need 31.1% gross margin just to cover overheads.</t>
+          <t>2 of the 6 installation jobs invoiced in September made less than the 35.0% job gross margin target. The Wacol warehouse switchboard made a 22.7% job gross margin: 150.0 h of technician time ($10,200) and $7,400 of subcontractors on a $52,400 job. Jobs need 39.0% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2858,7 @@
     <row r="104" ht="60" customHeight="1">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>3 installations under the 35.0% target, worth about $12,497 between them on $87,100 of revenue. The biggest gap, Wacol warehouse switchboard: 13.5% gross margin, 21.5 points under the 35.0% target: about $10,080 on $46,800 of revenue in September. It's below the 31.1% needed to cover overheads, too.</t>
+          <t>2 installations under the 35.0% target, worth about $6,513 between them on $83,100 of revenue. The biggest gap, Wacol warehouse switchboard: 22.7% gross margin, 12.3 points under the 35.0% target: about $6,440 on $52,400 of revenue in September. It's below the 39.0% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
@@ -2961,7 +2947,7 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>69.2% of call-out revenue</t>
+          <t>71.6% of call-out revenue</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3096,7 @@
     <row r="131" ht="60" customHeight="1">
       <c r="A131" s="3" t="inlineStr">
         <is>
-          <t>64 call-outs in September billed $21,543 of technician time and $9,594 of materials ($7,380 at cost plus 30%), and made a 43.9% job gross margin between them. Gross margins run from 37.6% to 47.1% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+          <t>64 call-outs in September billed $24,216 of technician time and $9,594 of materials ($7,380 at cost plus 30%), and made a 48.3% job gross margin between them. Gross margins run from 41.2% to 51.8% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3111,7 @@
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="3" t="inlineStr">
         <is>
-          <t>All call-outs: 43.9% gross margin, 8.9 points over the 35.0% target ($2,761 ahead on $31,137 in September).</t>
+          <t>All call-outs: 48.3% gross margin, 13.3 points over the 35.0% target ($4,499 ahead on $33,810 in September).</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3151,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3214,7 +3200,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3234,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>73107</v>
+        <v>96230</v>
       </c>
     </row>
     <row r="9">
@@ -3258,7 +3244,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>54600</v>
+        <v>79587</v>
       </c>
     </row>
     <row r="10">
@@ -3321,7 +3307,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
     </row>
     <row r="16">
@@ -3360,7 +3346,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -3400,10 +3386,10 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>179007</v>
+        <v>199523</v>
       </c>
     </row>
     <row r="26">
@@ -3485,10 +3471,10 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>179007</v>
+        <v>199523</v>
       </c>
     </row>
     <row r="35">
@@ -3565,7 +3551,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>73107</v>
+        <v>96230</v>
       </c>
     </row>
     <row r="44">
@@ -3575,7 +3561,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>54600</v>
+        <v>79587</v>
       </c>
     </row>
     <row r="45">
@@ -3638,7 +3624,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
     </row>
     <row r="51">
@@ -3677,7 +3663,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -3712,7 +3698,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="61">
@@ -3778,7 +3764,7 @@
         </is>
       </c>
       <c r="B69" s="13" t="n">
-        <v>130700</v>
+        <v>146300</v>
       </c>
     </row>
     <row r="70">
@@ -3844,7 +3830,7 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>31137</v>
+        <v>33810</v>
       </c>
     </row>
     <row r="79">
@@ -3915,10 +3901,10 @@
         </is>
       </c>
       <c r="B87" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="C87" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="88">
@@ -4000,10 +3986,10 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="C96" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="97">
@@ -4080,7 +4066,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>73107</v>
+        <v>96230</v>
       </c>
     </row>
     <row r="106">
@@ -4090,7 +4076,7 @@
         </is>
       </c>
       <c r="B106" s="13" t="n">
-        <v>54600</v>
+        <v>79587</v>
       </c>
     </row>
     <row r="107">
@@ -4153,7 +4139,7 @@
         </is>
       </c>
       <c r="B112" s="13" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
     </row>
     <row r="113">
@@ -4192,7 +4178,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4213,7 @@
         </is>
       </c>
       <c r="B122" s="13" t="n">
-        <v>1700</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="123">
@@ -4334,7 +4320,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>2200</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="136">
@@ -4415,7 +4401,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4427,7 @@
         </is>
       </c>
       <c r="B148" s="13" t="n">
-        <v>1800</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="149">
@@ -4451,7 +4437,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>-40</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="150">
@@ -4471,7 +4457,7 @@
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
@@ -4522,7 +4508,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4544,7 @@
         </is>
       </c>
       <c r="B162" s="13" t="n">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="163">
@@ -4578,7 +4564,7 @@
         </is>
       </c>
       <c r="B164" s="17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="165">
@@ -4629,7 +4615,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Newstead gym</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4641,7 @@
         </is>
       </c>
       <c r="B174" s="13" t="n">
-        <v>3400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="175">
@@ -4665,7 +4651,7 @@
         </is>
       </c>
       <c r="B175" s="13" t="n">
-        <v>-70</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="176">
@@ -4685,7 +4671,7 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
@@ -4736,7 +4722,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4748,7 @@
         </is>
       </c>
       <c r="B187" s="13" t="n">
-        <v>3200</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="188">
@@ -4772,7 +4758,7 @@
         </is>
       </c>
       <c r="B188" s="13" t="n">
-        <v>-60</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="189">
@@ -4792,7 +4778,7 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="191">
@@ -4843,7 +4829,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
@@ -4869,7 +4855,7 @@
         </is>
       </c>
       <c r="B200" s="13" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="201">
@@ -4879,7 +4865,7 @@
         </is>
       </c>
       <c r="B201" s="13" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="202">
@@ -4899,7 +4885,7 @@
         </is>
       </c>
       <c r="B203" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204">
@@ -4976,7 +4962,7 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>4100</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="214">
@@ -5057,7 +5043,7 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
+          <t>Bulimba school</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5069,7 @@
         </is>
       </c>
       <c r="B226" s="13" t="n">
-        <v>3000</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="227">
@@ -5093,7 +5079,7 @@
         </is>
       </c>
       <c r="B227" s="13" t="n">
-        <v>-70</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="228">
@@ -5113,7 +5099,7 @@
         </is>
       </c>
       <c r="B229" s="17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="230">
@@ -5164,7 +5150,7 @@
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Wacol logistics depot</t>
         </is>
       </c>
     </row>
@@ -5190,7 +5176,7 @@
         </is>
       </c>
       <c r="B239" s="13" t="n">
-        <v>4200</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="240">
@@ -5200,7 +5186,7 @@
         </is>
       </c>
       <c r="B240" s="13" t="n">
-        <v>-90</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="241">
@@ -5220,7 +5206,7 @@
         </is>
       </c>
       <c r="B242" s="17" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="243">
@@ -5271,7 +5257,7 @@
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5283,7 @@
         </is>
       </c>
       <c r="B252" s="13" t="n">
-        <v>2800</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="253">
@@ -5307,7 +5293,7 @@
         </is>
       </c>
       <c r="B253" s="13" t="n">
-        <v>-60</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="254">
@@ -5327,7 +5313,7 @@
         </is>
       </c>
       <c r="B255" s="17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="256">
@@ -5404,7 +5390,7 @@
         </is>
       </c>
       <c r="B265" s="13" t="n">
-        <v>2600</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="266">
@@ -5511,7 +5497,7 @@
         </is>
       </c>
       <c r="B278" s="13" t="n">
-        <v>3900</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="279">
@@ -5618,7 +5604,7 @@
         </is>
       </c>
       <c r="B291" s="13" t="n">
-        <v>2400</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="292">
@@ -5730,10 +5716,10 @@
         </is>
       </c>
       <c r="B304" s="13" t="n">
-        <v>130700</v>
+        <v>146300</v>
       </c>
       <c r="C304" s="13" t="n">
-        <v>109600</v>
+        <v>122800</v>
       </c>
     </row>
     <row r="305">
@@ -5815,10 +5801,10 @@
         </is>
       </c>
       <c r="B313" s="13" t="n">
-        <v>130700</v>
+        <v>146300</v>
       </c>
       <c r="C313" s="13" t="n">
-        <v>109600</v>
+        <v>122800</v>
       </c>
     </row>
     <row r="314">
@@ -5895,7 +5881,7 @@
         </is>
       </c>
       <c r="B322" s="13" t="n">
-        <v>73107</v>
+        <v>96230</v>
       </c>
     </row>
     <row r="323">
@@ -5905,7 +5891,7 @@
         </is>
       </c>
       <c r="B323" s="13" t="n">
-        <v>54600</v>
+        <v>79587</v>
       </c>
     </row>
     <row r="324">
@@ -5968,7 +5954,7 @@
         </is>
       </c>
       <c r="B329" s="13" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
     </row>
     <row r="330">
@@ -6007,7 +5993,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6028,7 @@
         </is>
       </c>
       <c r="B339" s="13" t="n">
-        <v>9800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="340">
@@ -6149,7 +6135,7 @@
         </is>
       </c>
       <c r="B352" s="13" t="n">
-        <v>18600</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="353">
@@ -6256,7 +6242,7 @@
         </is>
       </c>
       <c r="B365" s="13" t="n">
-        <v>15200</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="366">
@@ -6363,7 +6349,7 @@
         </is>
       </c>
       <c r="B378" s="13" t="n">
-        <v>12900</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="379">
@@ -6470,7 +6456,7 @@
         </is>
       </c>
       <c r="B391" s="13" t="n">
-        <v>27400</v>
+        <v>30700</v>
       </c>
     </row>
     <row r="392">
@@ -6577,7 +6563,7 @@
         </is>
       </c>
       <c r="B404" s="13" t="n">
-        <v>46800</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="405">
@@ -6689,10 +6675,10 @@
         </is>
       </c>
       <c r="B417" s="13" t="n">
-        <v>31137</v>
+        <v>33810</v>
       </c>
       <c r="C417" s="13" t="n">
-        <v>28907</v>
+        <v>31373</v>
       </c>
     </row>
     <row r="418">
@@ -6774,10 +6760,10 @@
         </is>
       </c>
       <c r="B426" s="13" t="n">
-        <v>31137</v>
+        <v>33810</v>
       </c>
       <c r="C426" s="13" t="n">
-        <v>28907</v>
+        <v>31373</v>
       </c>
     </row>
     <row r="427">
@@ -6854,7 +6840,7 @@
         </is>
       </c>
       <c r="B435" s="13" t="n">
-        <v>73107</v>
+        <v>96230</v>
       </c>
     </row>
     <row r="436">
@@ -6864,7 +6850,7 @@
         </is>
       </c>
       <c r="B436" s="13" t="n">
-        <v>54600</v>
+        <v>79587</v>
       </c>
     </row>
     <row r="437">
@@ -6927,7 +6913,7 @@
         </is>
       </c>
       <c r="B442" s="13" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
     </row>
     <row r="443">
@@ -6966,7 +6952,7 @@
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
         <is>
-          <t>Ties to the September 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the September 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6968,7 @@
     <row r="450">
       <c r="A450" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -6997,11 +6983,11 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B452" s="13" t="n">
-        <v>21543</v>
+        <v>24216</v>
       </c>
     </row>
     <row r="453">
@@ -7079,7 +7065,7 @@
     <row r="462">
       <c r="A462" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -7094,11 +7080,11 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B464" s="13" t="n">
-        <v>21543</v>
+        <v>24216</v>
       </c>
     </row>
     <row r="465">
@@ -7201,11 +7187,11 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B477" s="13" t="n">
-        <v>870</v>
+        <v>978</v>
       </c>
     </row>
     <row r="478">
@@ -7308,11 +7294,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B490" s="13" t="n">
-        <v>2834</v>
+        <v>3185</v>
       </c>
     </row>
     <row r="491">
@@ -7415,11 +7401,11 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B503" s="13" t="n">
-        <v>4930</v>
+        <v>5542</v>
       </c>
     </row>
     <row r="504">
@@ -7522,11 +7508,11 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B516" s="13" t="n">
-        <v>2904</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="517">
@@ -7629,11 +7615,11 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B529" s="13" t="n">
-        <v>4785</v>
+        <v>5379</v>
       </c>
     </row>
     <row r="530">
@@ -7736,11 +7722,11 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B542" s="13" t="n">
-        <v>5220</v>
+        <v>5868</v>
       </c>
     </row>
     <row r="543">
@@ -7815,7 +7801,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7890,13 +7876,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Report: Job gross margin by type of job, September 2026: Break-even 31.1%</t>
+          <t>Report: Job gross margin by type of job, September 2026: Break-even 39.0%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>0.311</v>
+        <v>0.39</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7904,7 +7890,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>0.311</v>
+        <v>0.39</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -7938,13 +7924,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on each maintenance contract, September 2026: Break-even 31.1%</t>
+          <t>Report: Job gross margin on each maintenance contract, September 2026: Break-even 39.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>0.311</v>
+        <v>0.39</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -7952,7 +7938,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>0.311</v>
+        <v>0.39</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -7986,13 +7972,13 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on each installation invoiced in September 2026: Break-even 31.1%</t>
+          <t>Report: Job gross margin on each installation invoiced in September 2026: Break-even 39.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>0.311</v>
+        <v>0.39</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -8000,7 +7986,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>0.311</v>
+        <v>0.39</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -8034,13 +8020,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on call-outs by length, September 2026: Break-even 31.1%</t>
+          <t>Report: Job gross margin on call-outs by length, September 2026: Break-even 39.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>0.311</v>
+        <v>0.39</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -8048,7 +8034,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>0.311</v>
+        <v>0.39</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -8094,7 +8080,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: September 2026 · Data status: Aug 2026 locked · Sep 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -8153,7 +8139,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>171009</v>
+        <v>191014</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>114334</v>
@@ -8184,7 +8170,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>179474</v>
+        <v>200124</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>113016</v>
@@ -8215,7 +8201,7 @@
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>143156</v>
+        <v>159406</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>85316</v>
@@ -8246,7 +8232,7 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>140909</v>
+        <v>156794</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>80742</v>
@@ -8277,7 +8263,7 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>160943</v>
+        <v>179190</v>
       </c>
       <c r="E10" s="13" t="n">
         <v>102348</v>
@@ -8308,7 +8294,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>135082</v>
+        <v>150465</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>85752</v>
@@ -8339,7 +8325,7 @@
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>124705</v>
+        <v>138865</v>
       </c>
       <c r="E12" s="13" t="n">
         <v>76808</v>
@@ -8370,7 +8356,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>129816</v>
+        <v>144649</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>83700</v>
@@ -8401,7 +8387,7 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>164113</v>
+        <v>183265</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>97584</v>
@@ -8432,7 +8418,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>120326</v>
@@ -8463,7 +8449,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>139164</v>
+        <v>155118</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>78258</v>
@@ -8494,7 +8480,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>80054</v>
@@ -8525,7 +8511,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>79452</v>
@@ -8556,7 +8542,7 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>174786</v>
+        <v>194966</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>115942</v>
@@ -8587,7 +8573,7 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>135079</v>
+        <v>150283</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>84626</v>
@@ -8618,7 +8604,7 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>106590</v>
@@ -8649,7 +8635,7 @@
         </is>
       </c>
       <c r="D22" s="13" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>120662</v>
@@ -8680,7 +8666,7 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>191500</v>
+        <v>213578</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>123342</v>
@@ -8711,7 +8697,7 @@
         </is>
       </c>
       <c r="D24" s="13" t="n">
-        <v>164987</v>
+        <v>183967</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>96144</v>
@@ -8742,7 +8728,7 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>98858</v>
@@ -8773,7 +8759,7 @@
         </is>
       </c>
       <c r="D26" s="13" t="n">
-        <v>173163</v>
+        <v>193032</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>106500</v>
@@ -8804,7 +8790,7 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>193245</v>
+        <v>215610</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>122124</v>
@@ -8835,7 +8821,7 @@
         </is>
       </c>
       <c r="D28" s="13" t="n">
-        <v>179007</v>
+        <v>199523</v>
       </c>
       <c r="E28" s="13" t="n">
         <v>105370</v>
@@ -8866,7 +8852,7 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>129230</v>
@@ -8897,7 +8883,7 @@
         </is>
       </c>
       <c r="D30" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>10420</v>
@@ -8928,7 +8914,7 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>10420</v>
@@ -8959,7 +8945,7 @@
         </is>
       </c>
       <c r="D32" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>10420</v>
@@ -8990,7 +8976,7 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>10420</v>
@@ -9021,7 +9007,7 @@
         </is>
       </c>
       <c r="D34" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E34" s="13" t="n">
         <v>11782</v>
@@ -9052,7 +9038,7 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>11782</v>
@@ -9083,7 +9069,7 @@
         </is>
       </c>
       <c r="D36" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E36" s="13" t="n">
         <v>11782</v>
@@ -9114,7 +9100,7 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>11782</v>
@@ -9145,7 +9131,7 @@
         </is>
       </c>
       <c r="D38" s="13" t="n">
-        <v>31870</v>
+        <v>35720</v>
       </c>
       <c r="E38" s="13" t="n">
         <v>13446</v>
@@ -9176,7 +9162,7 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>13446</v>
@@ -9207,7 +9193,7 @@
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E40" s="13" t="n">
         <v>13446</v>
@@ -9238,7 +9224,7 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>13446</v>
@@ -9269,7 +9255,7 @@
         </is>
       </c>
       <c r="D42" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E42" s="13" t="n">
         <v>14516</v>
@@ -9300,7 +9286,7 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E43" s="13" t="n">
         <v>14516</v>
@@ -9331,7 +9317,7 @@
         </is>
       </c>
       <c r="D44" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E44" s="13" t="n">
         <v>14516</v>
@@ -9362,7 +9348,7 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>14516</v>
@@ -9393,7 +9379,7 @@
         </is>
       </c>
       <c r="D46" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E46" s="13" t="n">
         <v>15158</v>
@@ -9424,7 +9410,7 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>15158</v>
@@ -9455,7 +9441,7 @@
         </is>
       </c>
       <c r="D48" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E48" s="13" t="n">
         <v>15158</v>
@@ -9486,7 +9472,7 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>16384</v>
@@ -9517,7 +9503,7 @@
         </is>
       </c>
       <c r="D50" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E50" s="13" t="n">
         <v>16384</v>
@@ -9548,7 +9534,7 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>16384</v>
@@ -9579,7 +9565,7 @@
         </is>
       </c>
       <c r="D52" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E52" s="13" t="n">
         <v>16384</v>
@@ -9610,7 +9596,7 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E53" s="13" t="n">
         <v>16384</v>
@@ -9641,7 +9627,7 @@
         </is>
       </c>
       <c r="D54" s="13" t="n">
-        <v>126300</v>
+        <v>141600</v>
       </c>
       <c r="E54" s="13" t="n">
         <v>92430</v>
@@ -9672,7 +9658,7 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>131400</v>
+        <v>147100</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>89070</v>
@@ -9703,7 +9689,7 @@
         </is>
       </c>
       <c r="D56" s="13" t="n">
-        <v>92600</v>
+        <v>103700</v>
       </c>
       <c r="E56" s="13" t="n">
         <v>59908</v>
@@ -9734,7 +9720,7 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>89400</v>
+        <v>100100</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>54678</v>
@@ -9765,7 +9751,7 @@
         </is>
       </c>
       <c r="D58" s="13" t="n">
-        <v>106000</v>
+        <v>118600</v>
       </c>
       <c r="E58" s="13" t="n">
         <v>74966</v>
@@ -9796,7 +9782,7 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>86100</v>
+        <v>96400</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>61664</v>
@@ -9827,7 +9813,7 @@
         </is>
       </c>
       <c r="D60" s="13" t="n">
-        <v>74900</v>
+        <v>83900</v>
       </c>
       <c r="E60" s="13" t="n">
         <v>52264</v>
@@ -9858,7 +9844,7 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>80300</v>
+        <v>89900</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>59534</v>
@@ -9889,7 +9875,7 @@
         </is>
       </c>
       <c r="D62" s="13" t="n">
-        <v>112700</v>
+        <v>126300</v>
       </c>
       <c r="E62" s="13" t="n">
         <v>72976</v>
@@ -9920,7 +9906,7 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>96920</v>
@@ -9951,7 +9937,7 @@
         </is>
       </c>
       <c r="D64" s="13" t="n">
-        <v>86200</v>
+        <v>96500</v>
       </c>
       <c r="E64" s="13" t="n">
         <v>53590</v>
@@ -9982,7 +9968,7 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>55440</v>
@@ -10013,7 +9999,7 @@
         </is>
       </c>
       <c r="D66" s="13" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="E66" s="13" t="n">
         <v>52288</v>
@@ -10044,7 +10030,7 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>113300</v>
+        <v>126900</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>87174</v>
@@ -10075,7 +10061,7 @@
         </is>
       </c>
       <c r="D68" s="13" t="n">
-        <v>69700</v>
+        <v>78100</v>
       </c>
       <c r="E68" s="13" t="n">
         <v>53408</v>
@@ -10106,7 +10092,7 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>74216</v>
@@ -10137,7 +10123,7 @@
         </is>
       </c>
       <c r="D70" s="13" t="n">
-        <v>129300</v>
+        <v>144800</v>
       </c>
       <c r="E70" s="13" t="n">
         <v>88896</v>
@@ -10168,7 +10154,7 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>129400</v>
+        <v>144900</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>94290</v>
@@ -10199,7 +10185,7 @@
         </is>
       </c>
       <c r="D72" s="13" t="n">
-        <v>104400</v>
+        <v>116900</v>
       </c>
       <c r="E72" s="13" t="n">
         <v>68016</v>
@@ -10230,7 +10216,7 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>92400</v>
+        <v>103400</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>66240</v>
@@ -10261,7 +10247,7 @@
         </is>
       </c>
       <c r="D74" s="13" t="n">
-        <v>103200</v>
+        <v>115600</v>
       </c>
       <c r="E74" s="13" t="n">
         <v>73792</v>
@@ -10292,7 +10278,7 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>127600</v>
+        <v>143000</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>91520</v>
@@ -10323,7 +10309,7 @@
         </is>
       </c>
       <c r="D76" s="13" t="n">
-        <v>109600</v>
+        <v>122800</v>
       </c>
       <c r="E76" s="13" t="n">
         <v>72720</v>
@@ -10354,7 +10340,7 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>130700</v>
+        <v>146300</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>95368</v>
@@ -10385,7 +10371,7 @@
         </is>
       </c>
       <c r="D78" s="13" t="n">
-        <v>20039</v>
+        <v>21764</v>
       </c>
       <c r="E78" s="13" t="n">
         <v>11484</v>
@@ -10416,7 +10402,7 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>23404</v>
+        <v>25374</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>13526</v>
@@ -10447,7 +10433,7 @@
         </is>
       </c>
       <c r="D80" s="13" t="n">
-        <v>25886</v>
+        <v>28056</v>
       </c>
       <c r="E80" s="13" t="n">
         <v>14988</v>
@@ -10478,7 +10464,7 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>26839</v>
+        <v>29044</v>
       </c>
       <c r="E81" s="13" t="n">
         <v>15644</v>
@@ -10509,7 +10495,7 @@
         </is>
       </c>
       <c r="D82" s="13" t="n">
-        <v>27013</v>
+        <v>29290</v>
       </c>
       <c r="E82" s="13" t="n">
         <v>15600</v>
@@ -10540,7 +10526,7 @@
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>21052</v>
+        <v>22765</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>12306</v>
@@ -10571,7 +10557,7 @@
         </is>
       </c>
       <c r="D84" s="13" t="n">
-        <v>21875</v>
+        <v>23665</v>
       </c>
       <c r="E84" s="13" t="n">
         <v>12762</v>
@@ -10602,7 +10588,7 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>21586</v>
+        <v>23449</v>
       </c>
       <c r="E85" s="13" t="n">
         <v>12384</v>
@@ -10633,7 +10619,7 @@
         </is>
       </c>
       <c r="D86" s="13" t="n">
-        <v>19543</v>
+        <v>21245</v>
       </c>
       <c r="E86" s="13" t="n">
         <v>11162</v>
@@ -10664,7 +10650,7 @@
         </is>
       </c>
       <c r="D87" s="13" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
       <c r="E87" s="13" t="n">
         <v>9960</v>
@@ -10695,7 +10681,7 @@
         </is>
       </c>
       <c r="D88" s="13" t="n">
-        <v>19764</v>
+        <v>21418</v>
       </c>
       <c r="E88" s="13" t="n">
         <v>11222</v>
@@ -10726,7 +10712,7 @@
         </is>
       </c>
       <c r="D89" s="13" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
       <c r="E89" s="13" t="n">
         <v>11168</v>
@@ -10757,7 +10743,7 @@
         </is>
       </c>
       <c r="D90" s="13" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="E90" s="13" t="n">
         <v>12648</v>
@@ -10788,7 +10774,7 @@
         </is>
       </c>
       <c r="D91" s="13" t="n">
-        <v>25686</v>
+        <v>27966</v>
       </c>
       <c r="E91" s="13" t="n">
         <v>14252</v>
@@ -10819,7 +10805,7 @@
         </is>
       </c>
       <c r="D92" s="13" t="n">
-        <v>29579</v>
+        <v>32083</v>
       </c>
       <c r="E92" s="13" t="n">
         <v>16702</v>
@@ -10850,7 +10836,7 @@
         </is>
       </c>
       <c r="D93" s="13" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
       <c r="E93" s="13" t="n">
         <v>17858</v>
@@ -10881,7 +10867,7 @@
         </is>
       </c>
       <c r="D94" s="13" t="n">
-        <v>29572</v>
+        <v>32108</v>
       </c>
       <c r="E94" s="13" t="n">
         <v>16608</v>
@@ -10912,7 +10898,7 @@
         </is>
       </c>
       <c r="D95" s="13" t="n">
-        <v>24600</v>
+        <v>26678</v>
       </c>
       <c r="E95" s="13" t="n">
         <v>13894</v>
@@ -10943,7 +10929,7 @@
         </is>
       </c>
       <c r="D96" s="13" t="n">
-        <v>23087</v>
+        <v>25067</v>
       </c>
       <c r="E96" s="13" t="n">
         <v>12970</v>
@@ -10974,7 +10960,7 @@
         </is>
       </c>
       <c r="D97" s="13" t="n">
-        <v>29063</v>
+        <v>31592</v>
       </c>
       <c r="E97" s="13" t="n">
         <v>16234</v>
@@ -11005,7 +10991,7 @@
         </is>
       </c>
       <c r="D98" s="13" t="n">
-        <v>29463</v>
+        <v>32082</v>
       </c>
       <c r="E98" s="13" t="n">
         <v>16324</v>
@@ -11036,7 +11022,7 @@
         </is>
       </c>
       <c r="D99" s="13" t="n">
-        <v>25145</v>
+        <v>27260</v>
       </c>
       <c r="E99" s="13" t="n">
         <v>14220</v>
@@ -11067,7 +11053,7 @@
         </is>
       </c>
       <c r="D100" s="13" t="n">
-        <v>28907</v>
+        <v>31373</v>
       </c>
       <c r="E100" s="13" t="n">
         <v>16266</v>
@@ -11098,7 +11084,7 @@
         </is>
       </c>
       <c r="D101" s="13" t="n">
-        <v>31137</v>
+        <v>33810</v>
       </c>
       <c r="E101" s="13" t="n">
         <v>17478</v>
@@ -11118,7 +11104,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
